--- a/document/expr10/データ探索.xlsx
+++ b/document/expr10/データ探索.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="189">
   <si>
     <t>grade</t>
   </si>
@@ -571,16 +572,78 @@
     <t>1T</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1T</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2T</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3T</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3F</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>勝式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>組番</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>頻度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>平均</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>払い戻し金額</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -588,13 +651,28 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -801,9 +879,238 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="45">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -838,9 +1145,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1047,13 +1351,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1063,6 +1360,16 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -1102,9 +1409,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1311,13 +1615,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1327,6 +1624,16 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
@@ -1367,235 +1674,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -1610,7 +1688,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="テーブル2" displayName="テーブル2" ref="A3:J608" totalsRowShown="0" headerRowDxfId="30" dataDxfId="31" headerRowBorderDxfId="43" tableBorderDxfId="44" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="テーブル2" displayName="テーブル2" ref="A3:J608" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
   <autoFilter ref="A3:J608">
     <filterColumn colId="1">
       <filters>
@@ -1622,64 +1700,64 @@
     <sortCondition ref="A7"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" name="sanrentanno" dataDxfId="41"/>
-    <tableColumn id="2" name="grade" dataDxfId="40"/>
-    <tableColumn id="3" name="cnt" dataDxfId="39"/>
-    <tableColumn id="4" name="min" dataDxfId="38"/>
-    <tableColumn id="5" name="max" dataDxfId="37"/>
-    <tableColumn id="6" name="avg" dataDxfId="36"/>
-    <tableColumn id="7" name="median" dataDxfId="35"/>
-    <tableColumn id="8" name="modl" dataDxfId="34"/>
-    <tableColumn id="9" name="median25" dataDxfId="33"/>
-    <tableColumn id="10" name="median75" dataDxfId="32"/>
+    <tableColumn id="1" name="sanrentanno" dataDxfId="39"/>
+    <tableColumn id="2" name="grade" dataDxfId="38"/>
+    <tableColumn id="3" name="cnt" dataDxfId="37"/>
+    <tableColumn id="4" name="min" dataDxfId="36"/>
+    <tableColumn id="5" name="max" dataDxfId="35"/>
+    <tableColumn id="6" name="avg" dataDxfId="34"/>
+    <tableColumn id="7" name="median" dataDxfId="33"/>
+    <tableColumn id="8" name="modl" dataDxfId="32"/>
+    <tableColumn id="9" name="median25" dataDxfId="31"/>
+    <tableColumn id="10" name="median75" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="テーブル3" displayName="テーブル3" ref="L3:U157" totalsRowShown="0" headerRowDxfId="15" dataDxfId="16" headerRowBorderDxfId="28" tableBorderDxfId="29" totalsRowBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="テーブル3" displayName="テーブル3" ref="L3:U157" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="L3:U157"/>
   <sortState ref="L7:U157">
     <sortCondition ref="L27"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" name="nirentanno" dataDxfId="26"/>
-    <tableColumn id="2" name="grade" dataDxfId="25"/>
-    <tableColumn id="3" name="cnt" dataDxfId="24"/>
-    <tableColumn id="4" name="min" dataDxfId="23"/>
-    <tableColumn id="5" name="max" dataDxfId="22"/>
-    <tableColumn id="6" name="avg" dataDxfId="21"/>
-    <tableColumn id="7" name="median" dataDxfId="20"/>
-    <tableColumn id="8" name="modl" dataDxfId="19"/>
-    <tableColumn id="9" name="median25" dataDxfId="18"/>
-    <tableColumn id="10" name="median75" dataDxfId="17"/>
+    <tableColumn id="1" name="nirentanno" dataDxfId="24"/>
+    <tableColumn id="2" name="grade" dataDxfId="23"/>
+    <tableColumn id="3" name="cnt" dataDxfId="22"/>
+    <tableColumn id="4" name="min" dataDxfId="21"/>
+    <tableColumn id="5" name="max" dataDxfId="20"/>
+    <tableColumn id="6" name="avg" dataDxfId="19"/>
+    <tableColumn id="7" name="median" dataDxfId="18"/>
+    <tableColumn id="8" name="modl" dataDxfId="17"/>
+    <tableColumn id="9" name="median25" dataDxfId="16"/>
+    <tableColumn id="10" name="median75" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="テーブル4" displayName="テーブル4" ref="W3:AF42" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="テーブル4" displayName="テーブル4" ref="W3:AF42" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="W3:AF42"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="tansyono" dataDxfId="11"/>
-    <tableColumn id="2" name="grade" dataDxfId="10"/>
-    <tableColumn id="3" name="cnt" dataDxfId="9"/>
-    <tableColumn id="4" name="min" dataDxfId="8"/>
-    <tableColumn id="5" name="max" dataDxfId="7"/>
-    <tableColumn id="6" name="avg" dataDxfId="6"/>
-    <tableColumn id="7" name="median" dataDxfId="5"/>
-    <tableColumn id="8" name="modl" dataDxfId="4"/>
-    <tableColumn id="9" name="median25" dataDxfId="3"/>
-    <tableColumn id="10" name="median75" dataDxfId="2"/>
+    <tableColumn id="1" name="tansyono" dataDxfId="9"/>
+    <tableColumn id="2" name="grade" dataDxfId="8"/>
+    <tableColumn id="3" name="cnt" dataDxfId="7"/>
+    <tableColumn id="4" name="min" dataDxfId="6"/>
+    <tableColumn id="5" name="max" dataDxfId="5"/>
+    <tableColumn id="6" name="avg" dataDxfId="4"/>
+    <tableColumn id="7" name="median" dataDxfId="3"/>
+    <tableColumn id="8" name="modl" dataDxfId="2"/>
+    <tableColumn id="9" name="median25" dataDxfId="1"/>
+    <tableColumn id="10" name="median75" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1966,25 +2044,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF608"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="7" max="7" width="9.375" customWidth="1"/>
-    <col min="9" max="10" width="11.625" customWidth="1"/>
-    <col min="12" max="12" width="12.875" customWidth="1"/>
-    <col min="18" max="18" width="9.375" customWidth="1"/>
-    <col min="20" max="21" width="11.625" customWidth="1"/>
-    <col min="23" max="23" width="11.375" customWidth="1"/>
-    <col min="29" max="29" width="9.375" customWidth="1"/>
-    <col min="31" max="32" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" customWidth="1"/>
+    <col min="9" max="10" width="11.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" customWidth="1"/>
+    <col min="20" max="21" width="11.6640625" customWidth="1"/>
+    <col min="23" max="23" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="9.33203125" customWidth="1"/>
+    <col min="31" max="32" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -1995,7 +2073,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="28.5">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
@@ -2087,7 +2165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:32" hidden="1">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -2179,7 +2257,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
@@ -2271,7 +2349,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:32" hidden="1">
+    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -2363,7 +2441,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>12</v>
       </c>
@@ -2455,7 +2533,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:32" hidden="1">
+    <row r="8" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -2547,7 +2625,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:32" hidden="1">
+    <row r="9" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
@@ -2639,7 +2717,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="10" spans="1:32" hidden="1">
+    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -2731,7 +2809,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:32" hidden="1">
+    <row r="11" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
@@ -2823,7 +2901,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>13</v>
       </c>
@@ -2915,7 +2993,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:32" hidden="1">
+    <row r="13" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
@@ -3007,7 +3085,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="14" spans="1:32" hidden="1">
+    <row r="14" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -3099,7 +3177,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="15" spans="1:32" hidden="1">
+    <row r="15" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -3191,7 +3269,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="16" spans="1:32" hidden="1">
+    <row r="16" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3283,7 +3361,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>14</v>
       </c>
@@ -3375,7 +3453,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="18" spans="1:32" hidden="1">
+    <row r="18" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
@@ -3467,7 +3545,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="19" spans="1:32" hidden="1">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
@@ -3559,7 +3637,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="20" spans="1:32" hidden="1">
+    <row r="20" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
@@ -3651,7 +3729,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="1:32" hidden="1">
+    <row r="21" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
@@ -3743,7 +3821,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>15</v>
       </c>
@@ -3835,7 +3913,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="23" spans="1:32" hidden="1">
+    <row r="23" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
@@ -3927,7 +4005,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="24" spans="1:32" hidden="1">
+    <row r="24" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>16</v>
       </c>
@@ -4019,7 +4097,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="25" spans="1:32" hidden="1">
+    <row r="25" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
@@ -4111,7 +4189,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="26" spans="1:32" hidden="1">
+    <row r="26" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>16</v>
       </c>
@@ -4203,7 +4281,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>16</v>
       </c>
@@ -4295,7 +4373,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="28" spans="1:32" hidden="1">
+    <row r="28" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>16</v>
       </c>
@@ -4387,7 +4465,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="29" spans="1:32" hidden="1">
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
@@ -4479,7 +4557,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="30" spans="1:32" hidden="1">
+    <row r="30" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>17</v>
       </c>
@@ -4571,7 +4649,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="31" spans="1:32" hidden="1">
+    <row r="31" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>17</v>
       </c>
@@ -4663,7 +4741,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>17</v>
       </c>
@@ -4755,7 +4833,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="33" spans="1:32" hidden="1">
+    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>17</v>
       </c>
@@ -4847,7 +4925,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="34" spans="1:32" hidden="1">
+    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>18</v>
       </c>
@@ -4939,7 +5017,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:32" hidden="1">
+    <row r="35" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>18</v>
       </c>
@@ -5031,7 +5109,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:32" hidden="1">
+    <row r="36" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>18</v>
       </c>
@@ -5123,7 +5201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>18</v>
       </c>
@@ -5215,7 +5293,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:32" hidden="1">
+    <row r="38" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>18</v>
       </c>
@@ -5307,7 +5385,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="1:32" hidden="1">
+    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>19</v>
       </c>
@@ -5399,7 +5477,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:32" hidden="1">
+    <row r="40" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>19</v>
       </c>
@@ -5491,7 +5569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:32" hidden="1">
+    <row r="41" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>19</v>
       </c>
@@ -5583,7 +5661,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>19</v>
       </c>
@@ -5675,7 +5753,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:32" hidden="1">
+    <row r="43" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>19</v>
       </c>
@@ -5737,7 +5815,7 @@
         <v>4250</v>
       </c>
     </row>
-    <row r="44" spans="1:32" hidden="1">
+    <row r="44" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>20</v>
       </c>
@@ -5799,7 +5877,7 @@
         <v>4910</v>
       </c>
     </row>
-    <row r="45" spans="1:32" hidden="1">
+    <row r="45" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>20</v>
       </c>
@@ -5861,7 +5939,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="46" spans="1:32" hidden="1">
+    <row r="46" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -5923,7 +6001,7 @@
         <v>4060</v>
       </c>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>20</v>
       </c>
@@ -5985,7 +6063,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="48" spans="1:32" hidden="1">
+    <row r="48" spans="1:32" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>20</v>
       </c>
@@ -6047,7 +6125,7 @@
         <v>5550</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1">
+    <row r="49" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>21</v>
       </c>
@@ -6109,7 +6187,7 @@
         <v>6210</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1">
+    <row r="50" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>21</v>
       </c>
@@ -6171,7 +6249,7 @@
         <v>5050</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1">
+    <row r="51" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>21</v>
       </c>
@@ -6233,7 +6311,7 @@
         <v>4430</v>
       </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>21</v>
       </c>
@@ -6295,7 +6373,7 @@
         <v>4130</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1">
+    <row r="53" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>21</v>
       </c>
@@ -6357,7 +6435,7 @@
         <v>8800</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1">
+    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>22</v>
       </c>
@@ -6419,7 +6497,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1">
+    <row r="55" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>22</v>
       </c>
@@ -6481,7 +6559,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="56" spans="1:21" hidden="1">
+    <row r="56" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>22</v>
       </c>
@@ -6543,7 +6621,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>22</v>
       </c>
@@ -6605,7 +6683,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>22</v>
       </c>
@@ -6667,7 +6745,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1">
+    <row r="59" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>23</v>
       </c>
@@ -6729,7 +6807,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1">
+    <row r="60" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>23</v>
       </c>
@@ -6791,7 +6869,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="61" spans="1:21" hidden="1">
+    <row r="61" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>23</v>
       </c>
@@ -6853,7 +6931,7 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>23</v>
       </c>
@@ -6915,7 +6993,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1">
+    <row r="63" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>23</v>
       </c>
@@ -6977,7 +7055,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1">
+    <row r="64" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>24</v>
       </c>
@@ -7039,7 +7117,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1">
+    <row r="65" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>24</v>
       </c>
@@ -7101,7 +7179,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1">
+    <row r="66" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>24</v>
       </c>
@@ -7163,7 +7241,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>24</v>
       </c>
@@ -7225,7 +7303,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1">
+    <row r="68" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>24</v>
       </c>
@@ -7287,7 +7365,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1">
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>25</v>
       </c>
@@ -7349,7 +7427,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1">
+    <row r="70" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>25</v>
       </c>
@@ -7411,7 +7489,7 @@
         <v>6240</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1">
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>25</v>
       </c>
@@ -7473,7 +7551,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>25</v>
       </c>
@@ -7535,7 +7613,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>25</v>
       </c>
@@ -7597,7 +7675,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>26</v>
       </c>
@@ -7659,7 +7737,7 @@
         <v>6050</v>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>26</v>
       </c>
@@ -7721,7 +7799,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>26</v>
       </c>
@@ -7783,7 +7861,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>26</v>
       </c>
@@ -7845,7 +7923,7 @@
         <v>4290</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>26</v>
       </c>
@@ -7907,7 +7985,7 @@
         <v>6420</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>27</v>
       </c>
@@ -7969,7 +8047,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>27</v>
       </c>
@@ -8031,7 +8109,7 @@
         <v>2710</v>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>27</v>
       </c>
@@ -8093,7 +8171,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>27</v>
       </c>
@@ -8155,7 +8233,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>27</v>
       </c>
@@ -8217,7 +8295,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>28</v>
       </c>
@@ -8279,7 +8357,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="85" spans="1:21" hidden="1">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>28</v>
       </c>
@@ -8341,7 +8419,7 @@
         <v>5330</v>
       </c>
     </row>
-    <row r="86" spans="1:21" hidden="1">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>28</v>
       </c>
@@ -8403,7 +8481,7 @@
         <v>3580</v>
       </c>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>28</v>
       </c>
@@ -8465,7 +8543,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="88" spans="1:21" hidden="1">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>28</v>
       </c>
@@ -8527,7 +8605,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="89" spans="1:21" hidden="1">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>29</v>
       </c>
@@ -8589,7 +8667,7 @@
         <v>5240</v>
       </c>
     </row>
-    <row r="90" spans="1:21" hidden="1">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>29</v>
       </c>
@@ -8651,7 +8729,7 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="91" spans="1:21" hidden="1">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>29</v>
       </c>
@@ -8713,7 +8791,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>29</v>
       </c>
@@ -8775,7 +8853,7 @@
         <v>3850</v>
       </c>
     </row>
-    <row r="93" spans="1:21" hidden="1">
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>29</v>
       </c>
@@ -8837,7 +8915,7 @@
         <v>4560</v>
       </c>
     </row>
-    <row r="94" spans="1:21" hidden="1">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>30</v>
       </c>
@@ -8899,7 +8977,7 @@
         <v>4170</v>
       </c>
     </row>
-    <row r="95" spans="1:21" hidden="1">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>30</v>
       </c>
@@ -8961,7 +9039,7 @@
         <v>4140</v>
       </c>
     </row>
-    <row r="96" spans="1:21" hidden="1">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>30</v>
       </c>
@@ -9023,7 +9101,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>30</v>
       </c>
@@ -9085,7 +9163,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="98" spans="1:21" hidden="1">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>30</v>
       </c>
@@ -9147,7 +9225,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="99" spans="1:21" hidden="1">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>31</v>
       </c>
@@ -9209,7 +9287,7 @@
         <v>5540</v>
       </c>
     </row>
-    <row r="100" spans="1:21" hidden="1">
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>31</v>
       </c>
@@ -9271,7 +9349,7 @@
         <v>5850</v>
       </c>
     </row>
-    <row r="101" spans="1:21" hidden="1">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>31</v>
       </c>
@@ -9333,7 +9411,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>31</v>
       </c>
@@ -9395,7 +9473,7 @@
         <v>4360</v>
       </c>
     </row>
-    <row r="103" spans="1:21" hidden="1">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>31</v>
       </c>
@@ -9457,7 +9535,7 @@
         <v>6960</v>
       </c>
     </row>
-    <row r="104" spans="1:21" hidden="1">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>32</v>
       </c>
@@ -9519,7 +9597,7 @@
         <v>4360</v>
       </c>
     </row>
-    <row r="105" spans="1:21" hidden="1">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>32</v>
       </c>
@@ -9581,7 +9659,7 @@
         <v>4270</v>
       </c>
     </row>
-    <row r="106" spans="1:21" hidden="1">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>32</v>
       </c>
@@ -9643,7 +9721,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>32</v>
       </c>
@@ -9705,7 +9783,7 @@
         <v>3840</v>
       </c>
     </row>
-    <row r="108" spans="1:21" hidden="1">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>32</v>
       </c>
@@ -9767,7 +9845,7 @@
         <v>4270</v>
       </c>
     </row>
-    <row r="109" spans="1:21" hidden="1">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>33</v>
       </c>
@@ -9829,7 +9907,7 @@
         <v>7870</v>
       </c>
     </row>
-    <row r="110" spans="1:21" hidden="1">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>33</v>
       </c>
@@ -9891,7 +9969,7 @@
         <v>6790</v>
       </c>
     </row>
-    <row r="111" spans="1:21" hidden="1">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>33</v>
       </c>
@@ -9953,7 +10031,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>33</v>
       </c>
@@ -10015,7 +10093,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="113" spans="1:21" hidden="1">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>33</v>
       </c>
@@ -10077,7 +10155,7 @@
         <v>8290</v>
       </c>
     </row>
-    <row r="114" spans="1:21" hidden="1">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>34</v>
       </c>
@@ -10139,7 +10217,7 @@
         <v>8910</v>
       </c>
     </row>
-    <row r="115" spans="1:21" hidden="1">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>34</v>
       </c>
@@ -10201,7 +10279,7 @@
         <v>7970</v>
       </c>
     </row>
-    <row r="116" spans="1:21" hidden="1">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>34</v>
       </c>
@@ -10263,7 +10341,7 @@
         <v>6220</v>
       </c>
     </row>
-    <row r="117" spans="1:21">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>34</v>
       </c>
@@ -10325,7 +10403,7 @@
         <v>5710</v>
       </c>
     </row>
-    <row r="118" spans="1:21" hidden="1">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>34</v>
       </c>
@@ -10387,7 +10465,7 @@
         <v>7900</v>
       </c>
     </row>
-    <row r="119" spans="1:21" hidden="1">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>35</v>
       </c>
@@ -10449,7 +10527,7 @@
         <v>7280</v>
       </c>
     </row>
-    <row r="120" spans="1:21" hidden="1">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>35</v>
       </c>
@@ -10511,7 +10589,7 @@
         <v>8650</v>
       </c>
     </row>
-    <row r="121" spans="1:21" hidden="1">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>35</v>
       </c>
@@ -10573,7 +10651,7 @@
         <v>5950</v>
       </c>
     </row>
-    <row r="122" spans="1:21">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>35</v>
       </c>
@@ -10635,7 +10713,7 @@
         <v>6180</v>
       </c>
     </row>
-    <row r="123" spans="1:21" hidden="1">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>35</v>
       </c>
@@ -10697,7 +10775,7 @@
         <v>8130</v>
       </c>
     </row>
-    <row r="124" spans="1:21" hidden="1">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>36</v>
       </c>
@@ -10759,7 +10837,7 @@
         <v>8980</v>
       </c>
     </row>
-    <row r="125" spans="1:21" hidden="1">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>36</v>
       </c>
@@ -10821,7 +10899,7 @@
         <v>9020</v>
       </c>
     </row>
-    <row r="126" spans="1:21" hidden="1">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>36</v>
       </c>
@@ -10883,7 +10961,7 @@
         <v>6580</v>
       </c>
     </row>
-    <row r="127" spans="1:21">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>36</v>
       </c>
@@ -10945,7 +11023,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="128" spans="1:21" hidden="1">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>36</v>
       </c>
@@ -11007,7 +11085,7 @@
         <v>9530</v>
       </c>
     </row>
-    <row r="129" spans="1:21" hidden="1">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>37</v>
       </c>
@@ -11069,7 +11147,7 @@
         <v>6540</v>
       </c>
     </row>
-    <row r="130" spans="1:21" hidden="1">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>37</v>
       </c>
@@ -11131,7 +11209,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="131" spans="1:21" hidden="1">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>37</v>
       </c>
@@ -11193,7 +11271,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="132" spans="1:21">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>37</v>
       </c>
@@ -11255,7 +11333,7 @@
         <v>4390</v>
       </c>
     </row>
-    <row r="133" spans="1:21" hidden="1">
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>37</v>
       </c>
@@ -11317,7 +11395,7 @@
         <v>8340</v>
       </c>
     </row>
-    <row r="134" spans="1:21" hidden="1">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>38</v>
       </c>
@@ -11379,7 +11457,7 @@
         <v>10480</v>
       </c>
     </row>
-    <row r="135" spans="1:21" hidden="1">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>38</v>
       </c>
@@ -11441,7 +11519,7 @@
         <v>7460</v>
       </c>
     </row>
-    <row r="136" spans="1:21" hidden="1">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>38</v>
       </c>
@@ -11503,7 +11581,7 @@
         <v>6710</v>
       </c>
     </row>
-    <row r="137" spans="1:21">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
         <v>38</v>
       </c>
@@ -11565,7 +11643,7 @@
         <v>6060</v>
       </c>
     </row>
-    <row r="138" spans="1:21" hidden="1">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>38</v>
       </c>
@@ -11627,7 +11705,7 @@
         <v>9960</v>
       </c>
     </row>
-    <row r="139" spans="1:21" hidden="1">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>39</v>
       </c>
@@ -11689,7 +11767,7 @@
         <v>12290</v>
       </c>
     </row>
-    <row r="140" spans="1:21" hidden="1">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>39</v>
       </c>
@@ -11751,7 +11829,7 @@
         <v>14460</v>
       </c>
     </row>
-    <row r="141" spans="1:21" hidden="1">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>39</v>
       </c>
@@ -11813,7 +11891,7 @@
         <v>7060</v>
       </c>
     </row>
-    <row r="142" spans="1:21">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>39</v>
       </c>
@@ -11875,7 +11953,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="143" spans="1:21" hidden="1">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
         <v>39</v>
       </c>
@@ -11937,7 +12015,7 @@
         <v>13540</v>
       </c>
     </row>
-    <row r="144" spans="1:21" hidden="1">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>40</v>
       </c>
@@ -11999,7 +12077,7 @@
         <v>12360</v>
       </c>
     </row>
-    <row r="145" spans="1:21" hidden="1">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>40</v>
       </c>
@@ -12061,7 +12139,7 @@
         <v>8970</v>
       </c>
     </row>
-    <row r="146" spans="1:21" hidden="1">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>40</v>
       </c>
@@ -12123,7 +12201,7 @@
         <v>7250</v>
       </c>
     </row>
-    <row r="147" spans="1:21">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
         <v>40</v>
       </c>
@@ -12185,7 +12263,7 @@
         <v>7310</v>
       </c>
     </row>
-    <row r="148" spans="1:21" hidden="1">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>40</v>
       </c>
@@ -12247,7 +12325,7 @@
         <v>12750</v>
       </c>
     </row>
-    <row r="149" spans="1:21" hidden="1">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>41</v>
       </c>
@@ -12309,7 +12387,7 @@
         <v>11460</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>41</v>
       </c>
@@ -12371,7 +12449,7 @@
         <v>13270</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1">
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>41</v>
       </c>
@@ -12433,7 +12511,7 @@
         <v>8620</v>
       </c>
     </row>
-    <row r="152" spans="1:21">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>41</v>
       </c>
@@ -12495,7 +12573,7 @@
         <v>8410</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1">
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>41</v>
       </c>
@@ -12557,7 +12635,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1">
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>42</v>
       </c>
@@ -12619,7 +12697,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1">
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>42</v>
       </c>
@@ -12681,7 +12759,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1">
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>42</v>
       </c>
@@ -12743,7 +12821,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="157" spans="1:21">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>42</v>
       </c>
@@ -12805,7 +12883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1">
+    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>42</v>
       </c>
@@ -12837,7 +12915,7 @@
         <v>13980</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1">
+    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>43</v>
       </c>
@@ -12869,7 +12947,7 @@
         <v>20760</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1">
+    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>43</v>
       </c>
@@ -12901,7 +12979,7 @@
         <v>24890</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
         <v>43</v>
       </c>
@@ -12933,7 +13011,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>43</v>
       </c>
@@ -12965,7 +13043,7 @@
         <v>11080</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>43</v>
       </c>
@@ -12997,7 +13075,7 @@
         <v>18360</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>44</v>
       </c>
@@ -13029,7 +13107,7 @@
         <v>17510</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>44</v>
       </c>
@@ -13061,7 +13139,7 @@
         <v>11930</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>44</v>
       </c>
@@ -13093,7 +13171,7 @@
         <v>15070</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
         <v>44</v>
       </c>
@@ -13125,7 +13203,7 @@
         <v>12950</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="5" t="s">
         <v>44</v>
       </c>
@@ -13157,7 +13235,7 @@
         <v>25590</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>45</v>
       </c>
@@ -13189,7 +13267,7 @@
         <v>20240</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>45</v>
       </c>
@@ -13221,7 +13299,7 @@
         <v>27850</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="5" t="s">
         <v>45</v>
       </c>
@@ -13253,7 +13331,7 @@
         <v>15330</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="5" t="s">
         <v>45</v>
       </c>
@@ -13285,7 +13363,7 @@
         <v>12700</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>45</v>
       </c>
@@ -13317,7 +13395,7 @@
         <v>16690</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>46</v>
       </c>
@@ -13349,7 +13427,7 @@
         <v>20230</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>46</v>
       </c>
@@ -13381,7 +13459,7 @@
         <v>15710</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="5" t="s">
         <v>46</v>
       </c>
@@ -13413,7 +13491,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>46</v>
       </c>
@@ -13445,7 +13523,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>46</v>
       </c>
@@ -13477,7 +13555,7 @@
         <v>27240</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="5" t="s">
         <v>47</v>
       </c>
@@ -13509,7 +13587,7 @@
         <v>24930</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="5" t="s">
         <v>47</v>
       </c>
@@ -13541,7 +13619,7 @@
         <v>21890</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="5" t="s">
         <v>47</v>
       </c>
@@ -13573,7 +13651,7 @@
         <v>24570</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>47</v>
       </c>
@@ -13605,7 +13683,7 @@
         <v>15460</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>47</v>
       </c>
@@ -13637,7 +13715,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="5" t="s">
         <v>48</v>
       </c>
@@ -13669,7 +13747,7 @@
         <v>23450</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="5" t="s">
         <v>48</v>
       </c>
@@ -13701,7 +13779,7 @@
         <v>18410</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>48</v>
       </c>
@@ -13733,7 +13811,7 @@
         <v>19440</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="5" t="s">
         <v>48</v>
       </c>
@@ -13765,7 +13843,7 @@
         <v>15290</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>48</v>
       </c>
@@ -13797,7 +13875,7 @@
         <v>27040</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="5" t="s">
         <v>49</v>
       </c>
@@ -13829,7 +13907,7 @@
         <v>32660</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>49</v>
       </c>
@@ -13861,7 +13939,7 @@
         <v>19570</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="5" t="s">
         <v>49</v>
       </c>
@@ -13893,7 +13971,7 @@
         <v>17870</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
         <v>49</v>
       </c>
@@ -13925,7 +14003,7 @@
         <v>15290</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="5" t="s">
         <v>49</v>
       </c>
@@ -13957,7 +14035,7 @@
         <v>50340</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>50</v>
       </c>
@@ -13989,7 +14067,7 @@
         <v>35390</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="5" t="s">
         <v>50</v>
       </c>
@@ -14021,7 +14099,7 @@
         <v>13170</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="5" t="s">
         <v>50</v>
       </c>
@@ -14053,7 +14131,7 @@
         <v>18190</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="5" t="s">
         <v>50</v>
       </c>
@@ -14085,7 +14163,7 @@
         <v>16590</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>50</v>
       </c>
@@ -14117,7 +14195,7 @@
         <v>50720</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="5" t="s">
         <v>51</v>
       </c>
@@ -14149,7 +14227,7 @@
         <v>27320</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="5" t="s">
         <v>51</v>
       </c>
@@ -14181,7 +14259,7 @@
         <v>10980</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="5" t="s">
         <v>51</v>
       </c>
@@ -14213,7 +14291,7 @@
         <v>18380</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="5" t="s">
         <v>51</v>
       </c>
@@ -14245,7 +14323,7 @@
         <v>21280</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="5" t="s">
         <v>51</v>
       </c>
@@ -14277,7 +14355,7 @@
         <v>36270</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="5" t="s">
         <v>52</v>
       </c>
@@ -14309,7 +14387,7 @@
         <v>7870</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>52</v>
       </c>
@@ -14341,7 +14419,7 @@
         <v>7300</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="5" t="s">
         <v>52</v>
       </c>
@@ -14373,7 +14451,7 @@
         <v>6920</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="5" t="s">
         <v>52</v>
       </c>
@@ -14405,7 +14483,7 @@
         <v>6720</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
         <v>52</v>
       </c>
@@ -14437,7 +14515,7 @@
         <v>7930</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>53</v>
       </c>
@@ -14469,7 +14547,7 @@
         <v>6900</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>53</v>
       </c>
@@ -14501,7 +14579,7 @@
         <v>8160</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>53</v>
       </c>
@@ -14533,7 +14611,7 @@
         <v>6110</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>53</v>
       </c>
@@ -14565,7 +14643,7 @@
         <v>5810</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>53</v>
       </c>
@@ -14597,7 +14675,7 @@
         <v>9170</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>54</v>
       </c>
@@ -14629,7 +14707,7 @@
         <v>8270</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>54</v>
       </c>
@@ -14661,7 +14739,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>54</v>
       </c>
@@ -14693,7 +14771,7 @@
         <v>6880</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>54</v>
       </c>
@@ -14725,7 +14803,7 @@
         <v>6920</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>54</v>
       </c>
@@ -14757,7 +14835,7 @@
         <v>8850</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>55</v>
       </c>
@@ -14789,7 +14867,7 @@
         <v>10890</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>55</v>
       </c>
@@ -14821,7 +14899,7 @@
         <v>12030</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="5" t="s">
         <v>55</v>
       </c>
@@ -14853,7 +14931,7 @@
         <v>9210</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
         <v>55</v>
       </c>
@@ -14885,7 +14963,7 @@
         <v>8600</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
         <v>55</v>
       </c>
@@ -14917,7 +14995,7 @@
         <v>9010</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
         <v>56</v>
       </c>
@@ -14949,7 +15027,7 @@
         <v>13490</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>56</v>
       </c>
@@ -14981,7 +15059,7 @@
         <v>13150</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>56</v>
       </c>
@@ -15013,7 +15091,7 @@
         <v>10510</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>56</v>
       </c>
@@ -15045,7 +15123,7 @@
         <v>10580</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>56</v>
       </c>
@@ -15077,7 +15155,7 @@
         <v>11250</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>57</v>
       </c>
@@ -15109,7 +15187,7 @@
         <v>16330</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>57</v>
       </c>
@@ -15141,7 +15219,7 @@
         <v>13950</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>57</v>
       </c>
@@ -15173,7 +15251,7 @@
         <v>12210</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>57</v>
       </c>
@@ -15205,7 +15283,7 @@
         <v>11230</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>57</v>
       </c>
@@ -15237,7 +15315,7 @@
         <v>23470</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>58</v>
       </c>
@@ -15269,7 +15347,7 @@
         <v>20940</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="5" t="s">
         <v>58</v>
       </c>
@@ -15301,7 +15379,7 @@
         <v>12980</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="5" t="s">
         <v>58</v>
       </c>
@@ -15333,7 +15411,7 @@
         <v>12460</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="5" t="s">
         <v>58</v>
       </c>
@@ -15365,7 +15443,7 @@
         <v>13160</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="5" t="s">
         <v>58</v>
       </c>
@@ -15397,7 +15475,7 @@
         <v>22060</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="5" t="s">
         <v>59</v>
       </c>
@@ -15429,7 +15507,7 @@
         <v>25800</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="5" t="s">
         <v>59</v>
       </c>
@@ -15461,7 +15539,7 @@
         <v>14900</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>59</v>
       </c>
@@ -15493,7 +15571,7 @@
         <v>14480</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="5" t="s">
         <v>59</v>
       </c>
@@ -15525,7 +15603,7 @@
         <v>14360</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="5" t="s">
         <v>59</v>
       </c>
@@ -15557,7 +15635,7 @@
         <v>23660</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="5" t="s">
         <v>60</v>
       </c>
@@ -15589,7 +15667,7 @@
         <v>10780</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="5" t="s">
         <v>60</v>
       </c>
@@ -15621,7 +15699,7 @@
         <v>13020</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="5" t="s">
         <v>60</v>
       </c>
@@ -15653,7 +15731,7 @@
         <v>9310</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="5" t="s">
         <v>60</v>
       </c>
@@ -15685,7 +15763,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="5" t="s">
         <v>60</v>
       </c>
@@ -15717,7 +15795,7 @@
         <v>8660</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>61</v>
       </c>
@@ -15749,7 +15827,7 @@
         <v>18810</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>61</v>
       </c>
@@ -15781,7 +15859,7 @@
         <v>20490</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>61</v>
       </c>
@@ -15813,7 +15891,7 @@
         <v>16080</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>61</v>
       </c>
@@ -15845,7 +15923,7 @@
         <v>12630</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>61</v>
       </c>
@@ -15877,7 +15955,7 @@
         <v>20020</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="5" t="s">
         <v>62</v>
       </c>
@@ -15909,7 +15987,7 @@
         <v>15980</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>62</v>
       </c>
@@ -15941,7 +16019,7 @@
         <v>17410</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>62</v>
       </c>
@@ -15973,7 +16051,7 @@
         <v>11610</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>62</v>
       </c>
@@ -16005,7 +16083,7 @@
         <v>10320</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>62</v>
       </c>
@@ -16037,7 +16115,7 @@
         <v>13780</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>63</v>
       </c>
@@ -16069,7 +16147,7 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>63</v>
       </c>
@@ -16101,7 +16179,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>63</v>
       </c>
@@ -16133,7 +16211,7 @@
         <v>12570</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>63</v>
       </c>
@@ -16165,7 +16243,7 @@
         <v>11750</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>63</v>
       </c>
@@ -16197,7 +16275,7 @@
         <v>16060</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="5" t="s">
         <v>64</v>
       </c>
@@ -16229,7 +16307,7 @@
         <v>18030</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>64</v>
       </c>
@@ -16261,7 +16339,7 @@
         <v>14870</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="5" t="s">
         <v>64</v>
       </c>
@@ -16293,7 +16371,7 @@
         <v>13260</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="5" t="s">
         <v>64</v>
       </c>
@@ -16325,7 +16403,7 @@
         <v>12470</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="5" t="s">
         <v>64</v>
       </c>
@@ -16357,7 +16435,7 @@
         <v>28010</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="5" t="s">
         <v>65</v>
       </c>
@@ -16389,7 +16467,7 @@
         <v>25540</v>
       </c>
     </row>
-    <row r="270" spans="1:10" hidden="1">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="5" t="s">
         <v>65</v>
       </c>
@@ -16421,7 +16499,7 @@
         <v>17100</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="5" t="s">
         <v>65</v>
       </c>
@@ -16453,7 +16531,7 @@
         <v>16700</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="5" t="s">
         <v>65</v>
       </c>
@@ -16485,7 +16563,7 @@
         <v>15820</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="5" t="s">
         <v>65</v>
       </c>
@@ -16517,7 +16595,7 @@
         <v>18820</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="5" t="s">
         <v>66</v>
       </c>
@@ -16549,7 +16627,7 @@
         <v>26310</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>66</v>
       </c>
@@ -16581,7 +16659,7 @@
         <v>43400</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="5" t="s">
         <v>66</v>
       </c>
@@ -16613,7 +16691,7 @@
         <v>16570</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="5" t="s">
         <v>66</v>
       </c>
@@ -16645,7 +16723,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="278" spans="1:10" hidden="1">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="5" t="s">
         <v>66</v>
       </c>
@@ -16677,7 +16755,7 @@
         <v>19840</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="5" t="s">
         <v>67</v>
       </c>
@@ -16709,7 +16787,7 @@
         <v>26130</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="5" t="s">
         <v>67</v>
       </c>
@@ -16741,7 +16819,7 @@
         <v>30520</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="5" t="s">
         <v>67</v>
       </c>
@@ -16773,7 +16851,7 @@
         <v>15430</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="5" t="s">
         <v>67</v>
       </c>
@@ -16805,7 +16883,7 @@
         <v>15500</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="5" t="s">
         <v>67</v>
       </c>
@@ -16837,7 +16915,7 @@
         <v>21520</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="5" t="s">
         <v>68</v>
       </c>
@@ -16869,7 +16947,7 @@
         <v>29470</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="5" t="s">
         <v>68</v>
       </c>
@@ -16901,7 +16979,7 @@
         <v>26380</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="5" t="s">
         <v>68</v>
       </c>
@@ -16933,7 +17011,7 @@
         <v>20230</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="5" t="s">
         <v>68</v>
       </c>
@@ -16965,7 +17043,7 @@
         <v>15880</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="5" t="s">
         <v>68</v>
       </c>
@@ -16997,7 +17075,7 @@
         <v>24740</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>69</v>
       </c>
@@ -17029,7 +17107,7 @@
         <v>30840</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="5" t="s">
         <v>69</v>
       </c>
@@ -17061,7 +17139,7 @@
         <v>44690</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="5" t="s">
         <v>69</v>
       </c>
@@ -17093,7 +17171,7 @@
         <v>21610</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="5" t="s">
         <v>69</v>
       </c>
@@ -17125,7 +17203,7 @@
         <v>19230</v>
       </c>
     </row>
-    <row r="293" spans="1:10" hidden="1">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>69</v>
       </c>
@@ -17157,7 +17235,7 @@
         <v>30540</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="5" t="s">
         <v>70</v>
       </c>
@@ -17189,7 +17267,7 @@
         <v>25060</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="5" t="s">
         <v>70</v>
       </c>
@@ -17221,7 +17299,7 @@
         <v>13790</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="5" t="s">
         <v>70</v>
       </c>
@@ -17253,7 +17331,7 @@
         <v>20800</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="5" t="s">
         <v>70</v>
       </c>
@@ -17285,7 +17363,7 @@
         <v>18150</v>
       </c>
     </row>
-    <row r="298" spans="1:10" hidden="1">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="5" t="s">
         <v>70</v>
       </c>
@@ -17317,7 +17395,7 @@
         <v>28320</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>71</v>
       </c>
@@ -17349,7 +17427,7 @@
         <v>20470</v>
       </c>
     </row>
-    <row r="300" spans="1:10" hidden="1">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="5" t="s">
         <v>71</v>
       </c>
@@ -17381,7 +17459,7 @@
         <v>16320</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="5" t="s">
         <v>71</v>
       </c>
@@ -17413,7 +17491,7 @@
         <v>18860</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="5" t="s">
         <v>71</v>
       </c>
@@ -17445,7 +17523,7 @@
         <v>19850</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="5" t="s">
         <v>71</v>
       </c>
@@ -17477,7 +17555,7 @@
         <v>33720</v>
       </c>
     </row>
-    <row r="304" spans="1:10" hidden="1">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="5" t="s">
         <v>72</v>
       </c>
@@ -17509,7 +17587,7 @@
         <v>8290</v>
       </c>
     </row>
-    <row r="305" spans="1:10" hidden="1">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="5" t="s">
         <v>72</v>
       </c>
@@ -17541,7 +17619,7 @@
         <v>8810</v>
       </c>
     </row>
-    <row r="306" spans="1:10" hidden="1">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="5" t="s">
         <v>72</v>
       </c>
@@ -17573,7 +17651,7 @@
         <v>7020</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="5" t="s">
         <v>72</v>
       </c>
@@ -17605,7 +17683,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="308" spans="1:10" hidden="1">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="5" t="s">
         <v>72</v>
       </c>
@@ -17637,7 +17715,7 @@
         <v>9410</v>
       </c>
     </row>
-    <row r="309" spans="1:10" hidden="1">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="5" t="s">
         <v>73</v>
       </c>
@@ -17669,7 +17747,7 @@
         <v>10740</v>
       </c>
     </row>
-    <row r="310" spans="1:10" hidden="1">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="5" t="s">
         <v>73</v>
       </c>
@@ -17701,7 +17779,7 @@
         <v>14490</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="5" t="s">
         <v>73</v>
       </c>
@@ -17733,7 +17811,7 @@
         <v>8770</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="5" t="s">
         <v>73</v>
       </c>
@@ -17765,7 +17843,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="5" t="s">
         <v>73</v>
       </c>
@@ -17797,7 +17875,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="314" spans="1:10" hidden="1">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="5" t="s">
         <v>74</v>
       </c>
@@ -17829,7 +17907,7 @@
         <v>8600</v>
       </c>
     </row>
-    <row r="315" spans="1:10" hidden="1">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="5" t="s">
         <v>74</v>
       </c>
@@ -17861,7 +17939,7 @@
         <v>9510</v>
       </c>
     </row>
-    <row r="316" spans="1:10" hidden="1">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="5" t="s">
         <v>74</v>
       </c>
@@ -17893,7 +17971,7 @@
         <v>7840</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="5" t="s">
         <v>74</v>
       </c>
@@ -17925,7 +18003,7 @@
         <v>7960</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="5" t="s">
         <v>74</v>
       </c>
@@ -17957,7 +18035,7 @@
         <v>10790</v>
       </c>
     </row>
-    <row r="319" spans="1:10" hidden="1">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="5" t="s">
         <v>75</v>
       </c>
@@ -17989,7 +18067,7 @@
         <v>11800</v>
       </c>
     </row>
-    <row r="320" spans="1:10" hidden="1">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="5" t="s">
         <v>75</v>
       </c>
@@ -18021,7 +18099,7 @@
         <v>16020</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="5" t="s">
         <v>75</v>
       </c>
@@ -18053,7 +18131,7 @@
         <v>9220</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="5" t="s">
         <v>75</v>
       </c>
@@ -18085,7 +18163,7 @@
         <v>9880</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="5" t="s">
         <v>75</v>
       </c>
@@ -18117,7 +18195,7 @@
         <v>13470</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="5" t="s">
         <v>76</v>
       </c>
@@ -18149,7 +18227,7 @@
         <v>15120</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="5" t="s">
         <v>76</v>
       </c>
@@ -18181,7 +18259,7 @@
         <v>14940</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="5" t="s">
         <v>76</v>
       </c>
@@ -18213,7 +18291,7 @@
         <v>12030</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="5" t="s">
         <v>76</v>
       </c>
@@ -18245,7 +18323,7 @@
         <v>10730</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="5" t="s">
         <v>76</v>
       </c>
@@ -18277,7 +18355,7 @@
         <v>14940</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="5" t="s">
         <v>77</v>
       </c>
@@ -18309,7 +18387,7 @@
         <v>21790</v>
       </c>
     </row>
-    <row r="330" spans="1:10" hidden="1">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="5" t="s">
         <v>77</v>
       </c>
@@ -18341,7 +18419,7 @@
         <v>22300</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="5" t="s">
         <v>77</v>
       </c>
@@ -18373,7 +18451,7 @@
         <v>14910</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="5" t="s">
         <v>77</v>
       </c>
@@ -18405,7 +18483,7 @@
         <v>13820</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="5" t="s">
         <v>77</v>
       </c>
@@ -18437,7 +18515,7 @@
         <v>30340</v>
       </c>
     </row>
-    <row r="334" spans="1:10" hidden="1">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="5" t="s">
         <v>78</v>
       </c>
@@ -18469,7 +18547,7 @@
         <v>21760</v>
       </c>
     </row>
-    <row r="335" spans="1:10" hidden="1">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>78</v>
       </c>
@@ -18501,7 +18579,7 @@
         <v>23150</v>
       </c>
     </row>
-    <row r="336" spans="1:10" hidden="1">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="5" t="s">
         <v>78</v>
       </c>
@@ -18533,7 +18611,7 @@
         <v>15290</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="5" t="s">
         <v>78</v>
       </c>
@@ -18565,7 +18643,7 @@
         <v>14080</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1">
+    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="5" t="s">
         <v>78</v>
       </c>
@@ -18597,7 +18675,7 @@
         <v>14440</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1">
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="5" t="s">
         <v>79</v>
       </c>
@@ -18629,7 +18707,7 @@
         <v>19960</v>
       </c>
     </row>
-    <row r="340" spans="1:10" hidden="1">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="5" t="s">
         <v>79</v>
       </c>
@@ -18661,7 +18739,7 @@
         <v>25340</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="5" t="s">
         <v>79</v>
       </c>
@@ -18693,7 +18771,7 @@
         <v>15070</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="5" t="s">
         <v>79</v>
       </c>
@@ -18725,7 +18803,7 @@
         <v>14970</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1">
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="5" t="s">
         <v>79</v>
       </c>
@@ -18757,7 +18835,7 @@
         <v>19120</v>
       </c>
     </row>
-    <row r="344" spans="1:10" hidden="1">
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="5" t="s">
         <v>80</v>
       </c>
@@ -18789,7 +18867,7 @@
         <v>17050</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1">
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="5" t="s">
         <v>80</v>
       </c>
@@ -18821,7 +18899,7 @@
         <v>15560</v>
       </c>
     </row>
-    <row r="346" spans="1:10" hidden="1">
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="5" t="s">
         <v>80</v>
       </c>
@@ -18853,7 +18931,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="5" t="s">
         <v>80</v>
       </c>
@@ -18885,7 +18963,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="348" spans="1:10" hidden="1">
+    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="5" t="s">
         <v>80</v>
       </c>
@@ -18917,7 +18995,7 @@
         <v>13470</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1">
+    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="5" t="s">
         <v>81</v>
       </c>
@@ -18949,7 +19027,7 @@
         <v>22980</v>
       </c>
     </row>
-    <row r="350" spans="1:10" hidden="1">
+    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="5" t="s">
         <v>81</v>
       </c>
@@ -18981,7 +19059,7 @@
         <v>30980</v>
       </c>
     </row>
-    <row r="351" spans="1:10" hidden="1">
+    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="5" t="s">
         <v>81</v>
       </c>
@@ -19013,7 +19091,7 @@
         <v>16510</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="5" t="s">
         <v>81</v>
       </c>
@@ -19045,7 +19123,7 @@
         <v>16070</v>
       </c>
     </row>
-    <row r="353" spans="1:10" hidden="1">
+    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="5" t="s">
         <v>81</v>
       </c>
@@ -19077,7 +19155,7 @@
         <v>21250</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1">
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>82</v>
       </c>
@@ -19109,7 +19187,7 @@
         <v>20480</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>82</v>
       </c>
@@ -19141,7 +19219,7 @@
         <v>23750</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>82</v>
       </c>
@@ -19173,7 +19251,7 @@
         <v>15330</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>82</v>
       </c>
@@ -19205,7 +19283,7 @@
         <v>15200</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>82</v>
       </c>
@@ -19237,7 +19315,7 @@
         <v>24520</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>83</v>
       </c>
@@ -19269,7 +19347,7 @@
         <v>24450</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>83</v>
       </c>
@@ -19301,7 +19379,7 @@
         <v>18120</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>83</v>
       </c>
@@ -19333,7 +19411,7 @@
         <v>17030</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>83</v>
       </c>
@@ -19365,7 +19443,7 @@
         <v>17900</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>83</v>
       </c>
@@ -19397,7 +19475,7 @@
         <v>21040</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>84</v>
       </c>
@@ -19429,7 +19507,7 @@
         <v>14480</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>84</v>
       </c>
@@ -19461,7 +19539,7 @@
         <v>7990</v>
       </c>
     </row>
-    <row r="366" spans="1:10" hidden="1">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>84</v>
       </c>
@@ -19493,7 +19571,7 @@
         <v>10920</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>84</v>
       </c>
@@ -19525,7 +19603,7 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>84</v>
       </c>
@@ -19557,7 +19635,7 @@
         <v>12250</v>
       </c>
     </row>
-    <row r="369" spans="1:10" hidden="1">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="5" t="s">
         <v>85</v>
       </c>
@@ -19589,7 +19667,7 @@
         <v>18290</v>
       </c>
     </row>
-    <row r="370" spans="1:10" hidden="1">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="5" t="s">
         <v>85</v>
       </c>
@@ -19621,7 +19699,7 @@
         <v>25990</v>
       </c>
     </row>
-    <row r="371" spans="1:10" hidden="1">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="5" t="s">
         <v>85</v>
       </c>
@@ -19653,7 +19731,7 @@
         <v>15790</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="5" t="s">
         <v>85</v>
       </c>
@@ -19685,7 +19763,7 @@
         <v>12990</v>
       </c>
     </row>
-    <row r="373" spans="1:10" hidden="1">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="5" t="s">
         <v>85</v>
       </c>
@@ -19717,7 +19795,7 @@
         <v>13810</v>
       </c>
     </row>
-    <row r="374" spans="1:10" hidden="1">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="5" t="s">
         <v>86</v>
       </c>
@@ -19749,7 +19827,7 @@
         <v>24260</v>
       </c>
     </row>
-    <row r="375" spans="1:10" hidden="1">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="5" t="s">
         <v>86</v>
       </c>
@@ -19781,7 +19859,7 @@
         <v>21840</v>
       </c>
     </row>
-    <row r="376" spans="1:10" hidden="1">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="5" t="s">
         <v>86</v>
       </c>
@@ -19813,7 +19891,7 @@
         <v>16960</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="5" t="s">
         <v>86</v>
       </c>
@@ -19845,7 +19923,7 @@
         <v>16880</v>
       </c>
     </row>
-    <row r="378" spans="1:10" hidden="1">
+    <row r="378" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>86</v>
       </c>
@@ -19877,7 +19955,7 @@
         <v>26360</v>
       </c>
     </row>
-    <row r="379" spans="1:10" hidden="1">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="5" t="s">
         <v>87</v>
       </c>
@@ -19909,7 +19987,7 @@
         <v>15110</v>
       </c>
     </row>
-    <row r="380" spans="1:10" hidden="1">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="5" t="s">
         <v>87</v>
       </c>
@@ -19941,7 +20019,7 @@
         <v>11420</v>
       </c>
     </row>
-    <row r="381" spans="1:10" hidden="1">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="5" t="s">
         <v>87</v>
       </c>
@@ -19973,7 +20051,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="5" t="s">
         <v>87</v>
       </c>
@@ -20005,7 +20083,7 @@
         <v>12730</v>
       </c>
     </row>
-    <row r="383" spans="1:10" hidden="1">
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="5" t="s">
         <v>87</v>
       </c>
@@ -20037,7 +20115,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="384" spans="1:10" hidden="1">
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="5" t="s">
         <v>88</v>
       </c>
@@ -20069,7 +20147,7 @@
         <v>21990</v>
       </c>
     </row>
-    <row r="385" spans="1:10" hidden="1">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="5" t="s">
         <v>88</v>
       </c>
@@ -20101,7 +20179,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="386" spans="1:10" hidden="1">
+    <row r="386" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="5" t="s">
         <v>88</v>
       </c>
@@ -20133,7 +20211,7 @@
         <v>16300</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="5" t="s">
         <v>88</v>
       </c>
@@ -20165,7 +20243,7 @@
         <v>15730</v>
       </c>
     </row>
-    <row r="388" spans="1:10" hidden="1">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="5" t="s">
         <v>88</v>
       </c>
@@ -20197,7 +20275,7 @@
         <v>29350</v>
       </c>
     </row>
-    <row r="389" spans="1:10" hidden="1">
+    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="5" t="s">
         <v>89</v>
       </c>
@@ -20229,7 +20307,7 @@
         <v>27840</v>
       </c>
     </row>
-    <row r="390" spans="1:10" hidden="1">
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="5" t="s">
         <v>89</v>
       </c>
@@ -20261,7 +20339,7 @@
         <v>31370</v>
       </c>
     </row>
-    <row r="391" spans="1:10" hidden="1">
+    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="5" t="s">
         <v>89</v>
       </c>
@@ -20293,7 +20371,7 @@
         <v>19320</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>89</v>
       </c>
@@ -20325,7 +20403,7 @@
         <v>17750</v>
       </c>
     </row>
-    <row r="393" spans="1:10" hidden="1">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>89</v>
       </c>
@@ -20357,7 +20435,7 @@
         <v>31400</v>
       </c>
     </row>
-    <row r="394" spans="1:10" hidden="1">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>90</v>
       </c>
@@ -20389,7 +20467,7 @@
         <v>36530</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>90</v>
       </c>
@@ -20421,7 +20499,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="5" t="s">
         <v>90</v>
       </c>
@@ -20453,7 +20531,7 @@
         <v>22240</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>90</v>
       </c>
@@ -20485,7 +20563,7 @@
         <v>20270</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="5" t="s">
         <v>90</v>
       </c>
@@ -20517,7 +20595,7 @@
         <v>25690</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="5" t="s">
         <v>91</v>
       </c>
@@ -20549,7 +20627,7 @@
         <v>23220</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>91</v>
       </c>
@@ -20581,7 +20659,7 @@
         <v>25830</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="5" t="s">
         <v>91</v>
       </c>
@@ -20613,7 +20691,7 @@
         <v>15610</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>91</v>
       </c>
@@ -20645,7 +20723,7 @@
         <v>18990</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>91</v>
       </c>
@@ -20677,7 +20755,7 @@
         <v>26690</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>92</v>
       </c>
@@ -20709,7 +20787,7 @@
         <v>16010</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>92</v>
       </c>
@@ -20741,7 +20819,7 @@
         <v>13860</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>92</v>
       </c>
@@ -20773,7 +20851,7 @@
         <v>15480</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>92</v>
       </c>
@@ -20805,7 +20883,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>92</v>
       </c>
@@ -20837,7 +20915,7 @@
         <v>14940</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>93</v>
       </c>
@@ -20869,7 +20947,7 @@
         <v>17940</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>93</v>
       </c>
@@ -20901,7 +20979,7 @@
         <v>20900</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>93</v>
       </c>
@@ -20933,7 +21011,7 @@
         <v>12930</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>93</v>
       </c>
@@ -20965,7 +21043,7 @@
         <v>14460</v>
       </c>
     </row>
-    <row r="413" spans="1:10" hidden="1">
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>93</v>
       </c>
@@ -20997,7 +21075,7 @@
         <v>18390</v>
       </c>
     </row>
-    <row r="414" spans="1:10" hidden="1">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>94</v>
       </c>
@@ -21029,7 +21107,7 @@
         <v>22910</v>
       </c>
     </row>
-    <row r="415" spans="1:10" hidden="1">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>94</v>
       </c>
@@ -21061,7 +21139,7 @@
         <v>21320</v>
       </c>
     </row>
-    <row r="416" spans="1:10" hidden="1">
+    <row r="416" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>94</v>
       </c>
@@ -21093,7 +21171,7 @@
         <v>15120</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>94</v>
       </c>
@@ -21125,7 +21203,7 @@
         <v>16610</v>
       </c>
     </row>
-    <row r="418" spans="1:10" hidden="1">
+    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>94</v>
       </c>
@@ -21157,7 +21235,7 @@
         <v>17810</v>
       </c>
     </row>
-    <row r="419" spans="1:10" hidden="1">
+    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>95</v>
       </c>
@@ -21189,7 +21267,7 @@
         <v>20450</v>
       </c>
     </row>
-    <row r="420" spans="1:10" hidden="1">
+    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>95</v>
       </c>
@@ -21221,7 +21299,7 @@
         <v>20460</v>
       </c>
     </row>
-    <row r="421" spans="1:10" hidden="1">
+    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>95</v>
       </c>
@@ -21253,7 +21331,7 @@
         <v>22020</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>95</v>
       </c>
@@ -21285,7 +21363,7 @@
         <v>17900</v>
       </c>
     </row>
-    <row r="423" spans="1:10" hidden="1">
+    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>95</v>
       </c>
@@ -21317,7 +21395,7 @@
         <v>19320</v>
       </c>
     </row>
-    <row r="424" spans="1:10" hidden="1">
+    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>96</v>
       </c>
@@ -21349,7 +21427,7 @@
         <v>25830</v>
       </c>
     </row>
-    <row r="425" spans="1:10" hidden="1">
+    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>96</v>
       </c>
@@ -21381,7 +21459,7 @@
         <v>28440</v>
       </c>
     </row>
-    <row r="426" spans="1:10" hidden="1">
+    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>96</v>
       </c>
@@ -21413,7 +21491,7 @@
         <v>18660</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>96</v>
       </c>
@@ -21445,7 +21523,7 @@
         <v>17230</v>
       </c>
     </row>
-    <row r="428" spans="1:10" hidden="1">
+    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>96</v>
       </c>
@@ -21477,7 +21555,7 @@
         <v>43870</v>
       </c>
     </row>
-    <row r="429" spans="1:10" hidden="1">
+    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>97</v>
       </c>
@@ -21509,7 +21587,7 @@
         <v>32800</v>
       </c>
     </row>
-    <row r="430" spans="1:10" hidden="1">
+    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>97</v>
       </c>
@@ -21541,7 +21619,7 @@
         <v>35390</v>
       </c>
     </row>
-    <row r="431" spans="1:10" hidden="1">
+    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>97</v>
       </c>
@@ -21573,7 +21651,7 @@
         <v>21600</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>97</v>
       </c>
@@ -21605,7 +21683,7 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="433" spans="1:10" hidden="1">
+    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>97</v>
       </c>
@@ -21637,7 +21715,7 @@
         <v>35490</v>
       </c>
     </row>
-    <row r="434" spans="1:10" hidden="1">
+    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>98</v>
       </c>
@@ -21669,7 +21747,7 @@
         <v>49450</v>
       </c>
     </row>
-    <row r="435" spans="1:10" hidden="1">
+    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>98</v>
       </c>
@@ -21701,7 +21779,7 @@
         <v>28350</v>
       </c>
     </row>
-    <row r="436" spans="1:10" hidden="1">
+    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>98</v>
       </c>
@@ -21733,7 +21811,7 @@
         <v>21880</v>
       </c>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>98</v>
       </c>
@@ -21765,7 +21843,7 @@
         <v>23790</v>
       </c>
     </row>
-    <row r="438" spans="1:10" hidden="1">
+    <row r="438" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="5" t="s">
         <v>98</v>
       </c>
@@ -21797,7 +21875,7 @@
         <v>56510</v>
       </c>
     </row>
-    <row r="439" spans="1:10" hidden="1">
+    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>99</v>
       </c>
@@ -21829,7 +21907,7 @@
         <v>35910</v>
       </c>
     </row>
-    <row r="440" spans="1:10" hidden="1">
+    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>99</v>
       </c>
@@ -21861,7 +21939,7 @@
         <v>42840</v>
       </c>
     </row>
-    <row r="441" spans="1:10" hidden="1">
+    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>99</v>
       </c>
@@ -21893,7 +21971,7 @@
         <v>23060</v>
       </c>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>99</v>
       </c>
@@ -21925,7 +22003,7 @@
         <v>23360</v>
       </c>
     </row>
-    <row r="443" spans="1:10" hidden="1">
+    <row r="443" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>99</v>
       </c>
@@ -21957,7 +22035,7 @@
         <v>36730</v>
       </c>
     </row>
-    <row r="444" spans="1:10" hidden="1">
+    <row r="444" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>100</v>
       </c>
@@ -21989,7 +22067,7 @@
         <v>20260</v>
       </c>
     </row>
-    <row r="445" spans="1:10" hidden="1">
+    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>100</v>
       </c>
@@ -22021,7 +22099,7 @@
         <v>34700</v>
       </c>
     </row>
-    <row r="446" spans="1:10" hidden="1">
+    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>100</v>
       </c>
@@ -22053,7 +22131,7 @@
         <v>19340</v>
       </c>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>100</v>
       </c>
@@ -22085,7 +22163,7 @@
         <v>18550</v>
       </c>
     </row>
-    <row r="448" spans="1:10" hidden="1">
+    <row r="448" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>100</v>
       </c>
@@ -22117,7 +22195,7 @@
         <v>20250</v>
       </c>
     </row>
-    <row r="449" spans="1:10" hidden="1">
+    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>101</v>
       </c>
@@ -22149,7 +22227,7 @@
         <v>48860</v>
       </c>
     </row>
-    <row r="450" spans="1:10" hidden="1">
+    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>101</v>
       </c>
@@ -22181,7 +22259,7 @@
         <v>25490</v>
       </c>
     </row>
-    <row r="451" spans="1:10" hidden="1">
+    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
         <v>101</v>
       </c>
@@ -22213,7 +22291,7 @@
         <v>23450</v>
       </c>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
         <v>101</v>
       </c>
@@ -22245,7 +22323,7 @@
         <v>21840</v>
       </c>
     </row>
-    <row r="453" spans="1:10" hidden="1">
+    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
         <v>101</v>
       </c>
@@ -22277,7 +22355,7 @@
         <v>46420</v>
       </c>
     </row>
-    <row r="454" spans="1:10" hidden="1">
+    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
         <v>102</v>
       </c>
@@ -22309,7 +22387,7 @@
         <v>37200</v>
       </c>
     </row>
-    <row r="455" spans="1:10" hidden="1">
+    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
         <v>102</v>
       </c>
@@ -22341,7 +22419,7 @@
         <v>25650</v>
       </c>
     </row>
-    <row r="456" spans="1:10" hidden="1">
+    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
         <v>102</v>
       </c>
@@ -22373,7 +22451,7 @@
         <v>33860</v>
       </c>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
         <v>102</v>
       </c>
@@ -22405,7 +22483,7 @@
         <v>25010</v>
       </c>
     </row>
-    <row r="458" spans="1:10" hidden="1">
+    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
         <v>102</v>
       </c>
@@ -22437,7 +22515,7 @@
         <v>30160</v>
       </c>
     </row>
-    <row r="459" spans="1:10" hidden="1">
+    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="5" t="s">
         <v>103</v>
       </c>
@@ -22469,7 +22547,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="460" spans="1:10" hidden="1">
+    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="5" t="s">
         <v>103</v>
       </c>
@@ -22501,7 +22579,7 @@
         <v>39380</v>
       </c>
     </row>
-    <row r="461" spans="1:10" hidden="1">
+    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="5" t="s">
         <v>103</v>
       </c>
@@ -22533,7 +22611,7 @@
         <v>25440</v>
       </c>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>103</v>
       </c>
@@ -22565,7 +22643,7 @@
         <v>26320</v>
       </c>
     </row>
-    <row r="463" spans="1:10" hidden="1">
+    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="5" t="s">
         <v>103</v>
       </c>
@@ -22597,7 +22675,7 @@
         <v>31700</v>
       </c>
     </row>
-    <row r="464" spans="1:10" hidden="1">
+    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="5" t="s">
         <v>104</v>
       </c>
@@ -22629,7 +22707,7 @@
         <v>25510</v>
       </c>
     </row>
-    <row r="465" spans="1:10" hidden="1">
+    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="5" t="s">
         <v>104</v>
       </c>
@@ -22661,7 +22739,7 @@
         <v>23220</v>
       </c>
     </row>
-    <row r="466" spans="1:10" hidden="1">
+    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="5" t="s">
         <v>104</v>
       </c>
@@ -22693,7 +22771,7 @@
         <v>22690</v>
       </c>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="5" t="s">
         <v>104</v>
       </c>
@@ -22725,7 +22803,7 @@
         <v>20980</v>
       </c>
     </row>
-    <row r="468" spans="1:10" hidden="1">
+    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="5" t="s">
         <v>104</v>
       </c>
@@ -22757,7 +22835,7 @@
         <v>55850</v>
       </c>
     </row>
-    <row r="469" spans="1:10" hidden="1">
+    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="5" t="s">
         <v>105</v>
       </c>
@@ -22789,7 +22867,7 @@
         <v>29210</v>
       </c>
     </row>
-    <row r="470" spans="1:10" hidden="1">
+    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="5" t="s">
         <v>105</v>
       </c>
@@ -22821,7 +22899,7 @@
         <v>35120</v>
       </c>
     </row>
-    <row r="471" spans="1:10" hidden="1">
+    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="5" t="s">
         <v>105</v>
       </c>
@@ -22853,7 +22931,7 @@
         <v>25350</v>
       </c>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="5" t="s">
         <v>105</v>
       </c>
@@ -22885,7 +22963,7 @@
         <v>25640</v>
       </c>
     </row>
-    <row r="473" spans="1:10" hidden="1">
+    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="5" t="s">
         <v>105</v>
       </c>
@@ -22917,7 +22995,7 @@
         <v>27210</v>
       </c>
     </row>
-    <row r="474" spans="1:10" hidden="1">
+    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="5" t="s">
         <v>106</v>
       </c>
@@ -22949,7 +23027,7 @@
         <v>34270</v>
       </c>
     </row>
-    <row r="475" spans="1:10" hidden="1">
+    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="5" t="s">
         <v>106</v>
       </c>
@@ -22981,7 +23059,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="476" spans="1:10" hidden="1">
+    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="5" t="s">
         <v>106</v>
       </c>
@@ -23013,7 +23091,7 @@
         <v>30250</v>
       </c>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="5" t="s">
         <v>106</v>
       </c>
@@ -23045,7 +23123,7 @@
         <v>30190</v>
       </c>
     </row>
-    <row r="478" spans="1:10" hidden="1">
+    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="5" t="s">
         <v>106</v>
       </c>
@@ -23077,7 +23155,7 @@
         <v>55230</v>
       </c>
     </row>
-    <row r="479" spans="1:10" hidden="1">
+    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>107</v>
       </c>
@@ -23109,7 +23187,7 @@
         <v>29300</v>
       </c>
     </row>
-    <row r="480" spans="1:10" hidden="1">
+    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="5" t="s">
         <v>107</v>
       </c>
@@ -23141,7 +23219,7 @@
         <v>48130</v>
       </c>
     </row>
-    <row r="481" spans="1:10" hidden="1">
+    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="5" t="s">
         <v>107</v>
       </c>
@@ -23173,7 +23251,7 @@
         <v>20770</v>
       </c>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="5" t="s">
         <v>107</v>
       </c>
@@ -23205,7 +23283,7 @@
         <v>24580</v>
       </c>
     </row>
-    <row r="483" spans="1:10" hidden="1">
+    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="5" t="s">
         <v>107</v>
       </c>
@@ -23237,7 +23315,7 @@
         <v>25550</v>
       </c>
     </row>
-    <row r="484" spans="1:10" hidden="1">
+    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="5" t="s">
         <v>108</v>
       </c>
@@ -23269,7 +23347,7 @@
         <v>37830</v>
       </c>
     </row>
-    <row r="485" spans="1:10" hidden="1">
+    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="5" t="s">
         <v>108</v>
       </c>
@@ -23301,7 +23379,7 @@
         <v>48410</v>
       </c>
     </row>
-    <row r="486" spans="1:10" hidden="1">
+    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="5" t="s">
         <v>108</v>
       </c>
@@ -23333,7 +23411,7 @@
         <v>22670</v>
       </c>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="5" t="s">
         <v>108</v>
       </c>
@@ -23365,7 +23443,7 @@
         <v>25520</v>
       </c>
     </row>
-    <row r="488" spans="1:10" hidden="1">
+    <row r="488" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="5" t="s">
         <v>108</v>
       </c>
@@ -23397,7 +23475,7 @@
         <v>29510</v>
       </c>
     </row>
-    <row r="489" spans="1:10" hidden="1">
+    <row r="489" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="5" t="s">
         <v>109</v>
       </c>
@@ -23429,7 +23507,7 @@
         <v>37950</v>
       </c>
     </row>
-    <row r="490" spans="1:10" hidden="1">
+    <row r="490" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="5" t="s">
         <v>109</v>
       </c>
@@ -23461,7 +23539,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="491" spans="1:10" hidden="1">
+    <row r="491" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="5" t="s">
         <v>109</v>
       </c>
@@ -23493,7 +23571,7 @@
         <v>26880</v>
       </c>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="5" t="s">
         <v>109</v>
       </c>
@@ -23525,7 +23603,7 @@
         <v>27440</v>
       </c>
     </row>
-    <row r="493" spans="1:10" hidden="1">
+    <row r="493" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="5" t="s">
         <v>109</v>
       </c>
@@ -23557,7 +23635,7 @@
         <v>46680</v>
       </c>
     </row>
-    <row r="494" spans="1:10" hidden="1">
+    <row r="494" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="5" t="s">
         <v>110</v>
       </c>
@@ -23589,7 +23667,7 @@
         <v>43630</v>
       </c>
     </row>
-    <row r="495" spans="1:10" hidden="1">
+    <row r="495" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="5" t="s">
         <v>110</v>
       </c>
@@ -23621,7 +23699,7 @@
         <v>66790</v>
       </c>
     </row>
-    <row r="496" spans="1:10" hidden="1">
+    <row r="496" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="5" t="s">
         <v>110</v>
       </c>
@@ -23653,7 +23731,7 @@
         <v>28140</v>
       </c>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="5" t="s">
         <v>110</v>
       </c>
@@ -23685,7 +23763,7 @@
         <v>28520</v>
       </c>
     </row>
-    <row r="498" spans="1:10" hidden="1">
+    <row r="498" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="5" t="s">
         <v>110</v>
       </c>
@@ -23717,7 +23795,7 @@
         <v>43470</v>
       </c>
     </row>
-    <row r="499" spans="1:10" hidden="1">
+    <row r="499" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="5" t="s">
         <v>111</v>
       </c>
@@ -23749,7 +23827,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="500" spans="1:10" hidden="1">
+    <row r="500" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="5" t="s">
         <v>111</v>
       </c>
@@ -23781,7 +23859,7 @@
         <v>18610</v>
       </c>
     </row>
-    <row r="501" spans="1:10" hidden="1">
+    <row r="501" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="5" t="s">
         <v>111</v>
       </c>
@@ -23813,7 +23891,7 @@
         <v>28390</v>
       </c>
     </row>
-    <row r="502" spans="1:10">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" s="5" t="s">
         <v>111</v>
       </c>
@@ -23845,7 +23923,7 @@
         <v>28550</v>
       </c>
     </row>
-    <row r="503" spans="1:10" hidden="1">
+    <row r="503" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="5" t="s">
         <v>111</v>
       </c>
@@ -23877,7 +23955,7 @@
         <v>49600</v>
       </c>
     </row>
-    <row r="504" spans="1:10" hidden="1">
+    <row r="504" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="5" t="s">
         <v>112</v>
       </c>
@@ -23909,7 +23987,7 @@
         <v>27260</v>
       </c>
     </row>
-    <row r="505" spans="1:10" hidden="1">
+    <row r="505" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="5" t="s">
         <v>112</v>
       </c>
@@ -23941,7 +24019,7 @@
         <v>25910</v>
       </c>
     </row>
-    <row r="506" spans="1:10" hidden="1">
+    <row r="506" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="5" t="s">
         <v>112</v>
       </c>
@@ -23973,7 +24051,7 @@
         <v>19400</v>
       </c>
     </row>
-    <row r="507" spans="1:10">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" s="5" t="s">
         <v>112</v>
       </c>
@@ -24005,7 +24083,7 @@
         <v>15320</v>
       </c>
     </row>
-    <row r="508" spans="1:10" hidden="1">
+    <row r="508" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="5" t="s">
         <v>112</v>
       </c>
@@ -24037,7 +24115,7 @@
         <v>38490</v>
       </c>
     </row>
-    <row r="509" spans="1:10" hidden="1">
+    <row r="509" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="5" t="s">
         <v>113</v>
       </c>
@@ -24069,7 +24147,7 @@
         <v>19580</v>
       </c>
     </row>
-    <row r="510" spans="1:10" hidden="1">
+    <row r="510" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="5" t="s">
         <v>113</v>
       </c>
@@ -24101,7 +24179,7 @@
         <v>20630</v>
       </c>
     </row>
-    <row r="511" spans="1:10" hidden="1">
+    <row r="511" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="5" t="s">
         <v>113</v>
       </c>
@@ -24133,7 +24211,7 @@
         <v>21820</v>
       </c>
     </row>
-    <row r="512" spans="1:10">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="5" t="s">
         <v>113</v>
       </c>
@@ -24165,7 +24243,7 @@
         <v>16780</v>
       </c>
     </row>
-    <row r="513" spans="1:10" hidden="1">
+    <row r="513" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="5" t="s">
         <v>113</v>
       </c>
@@ -24197,7 +24275,7 @@
         <v>29590</v>
       </c>
     </row>
-    <row r="514" spans="1:10" hidden="1">
+    <row r="514" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="5" t="s">
         <v>114</v>
       </c>
@@ -24229,7 +24307,7 @@
         <v>27150</v>
       </c>
     </row>
-    <row r="515" spans="1:10" hidden="1">
+    <row r="515" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="5" t="s">
         <v>114</v>
       </c>
@@ -24261,7 +24339,7 @@
         <v>42570</v>
       </c>
     </row>
-    <row r="516" spans="1:10" hidden="1">
+    <row r="516" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="5" t="s">
         <v>114</v>
       </c>
@@ -24293,7 +24371,7 @@
         <v>20670</v>
       </c>
     </row>
-    <row r="517" spans="1:10">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="5" t="s">
         <v>114</v>
       </c>
@@ -24325,7 +24403,7 @@
         <v>19480</v>
       </c>
     </row>
-    <row r="518" spans="1:10" hidden="1">
+    <row r="518" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="5" t="s">
         <v>114</v>
       </c>
@@ -24357,7 +24435,7 @@
         <v>39050</v>
       </c>
     </row>
-    <row r="519" spans="1:10" hidden="1">
+    <row r="519" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="5" t="s">
         <v>115</v>
       </c>
@@ -24389,7 +24467,7 @@
         <v>42770</v>
       </c>
     </row>
-    <row r="520" spans="1:10" hidden="1">
+    <row r="520" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="5" t="s">
         <v>115</v>
       </c>
@@ -24421,7 +24499,7 @@
         <v>33300</v>
       </c>
     </row>
-    <row r="521" spans="1:10" hidden="1">
+    <row r="521" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="5" t="s">
         <v>115</v>
       </c>
@@ -24453,7 +24531,7 @@
         <v>24740</v>
       </c>
     </row>
-    <row r="522" spans="1:10">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" s="5" t="s">
         <v>115</v>
       </c>
@@ -24485,7 +24563,7 @@
         <v>23580</v>
       </c>
     </row>
-    <row r="523" spans="1:10" hidden="1">
+    <row r="523" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="5" t="s">
         <v>115</v>
       </c>
@@ -24517,7 +24595,7 @@
         <v>35650</v>
       </c>
     </row>
-    <row r="524" spans="1:10" hidden="1">
+    <row r="524" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="5" t="s">
         <v>116</v>
       </c>
@@ -24549,7 +24627,7 @@
         <v>29870</v>
       </c>
     </row>
-    <row r="525" spans="1:10" hidden="1">
+    <row r="525" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="5" t="s">
         <v>116</v>
       </c>
@@ -24581,7 +24659,7 @@
         <v>15020</v>
       </c>
     </row>
-    <row r="526" spans="1:10" hidden="1">
+    <row r="526" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="5" t="s">
         <v>116</v>
       </c>
@@ -24613,7 +24691,7 @@
         <v>25300</v>
       </c>
     </row>
-    <row r="527" spans="1:10">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="5" t="s">
         <v>116</v>
       </c>
@@ -24645,7 +24723,7 @@
         <v>20890</v>
       </c>
     </row>
-    <row r="528" spans="1:10" hidden="1">
+    <row r="528" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="5" t="s">
         <v>116</v>
       </c>
@@ -24677,7 +24755,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="529" spans="1:10" hidden="1">
+    <row r="529" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="5" t="s">
         <v>117</v>
       </c>
@@ -24709,7 +24787,7 @@
         <v>44040</v>
       </c>
     </row>
-    <row r="530" spans="1:10" hidden="1">
+    <row r="530" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="5" t="s">
         <v>117</v>
       </c>
@@ -24741,7 +24819,7 @@
         <v>9410</v>
       </c>
     </row>
-    <row r="531" spans="1:10" hidden="1">
+    <row r="531" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="5" t="s">
         <v>117</v>
       </c>
@@ -24773,7 +24851,7 @@
         <v>20130</v>
       </c>
     </row>
-    <row r="532" spans="1:10">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A532" s="5" t="s">
         <v>117</v>
       </c>
@@ -24805,7 +24883,7 @@
         <v>20660</v>
       </c>
     </row>
-    <row r="533" spans="1:10" hidden="1">
+    <row r="533" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="5" t="s">
         <v>117</v>
       </c>
@@ -24837,7 +24915,7 @@
         <v>31670</v>
       </c>
     </row>
-    <row r="534" spans="1:10" hidden="1">
+    <row r="534" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="5" t="s">
         <v>118</v>
       </c>
@@ -24869,7 +24947,7 @@
         <v>49580</v>
       </c>
     </row>
-    <row r="535" spans="1:10" hidden="1">
+    <row r="535" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="5" t="s">
         <v>118</v>
       </c>
@@ -24901,7 +24979,7 @@
         <v>22160</v>
       </c>
     </row>
-    <row r="536" spans="1:10" hidden="1">
+    <row r="536" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="5" t="s">
         <v>118</v>
       </c>
@@ -24933,7 +25011,7 @@
         <v>35400</v>
       </c>
     </row>
-    <row r="537" spans="1:10">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="5" t="s">
         <v>118</v>
       </c>
@@ -24965,7 +25043,7 @@
         <v>26650</v>
       </c>
     </row>
-    <row r="538" spans="1:10" hidden="1">
+    <row r="538" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="5" t="s">
         <v>118</v>
       </c>
@@ -24997,7 +25075,7 @@
         <v>69170</v>
       </c>
     </row>
-    <row r="539" spans="1:10" hidden="1">
+    <row r="539" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="5" t="s">
         <v>119</v>
       </c>
@@ -25029,7 +25107,7 @@
         <v>55260</v>
       </c>
     </row>
-    <row r="540" spans="1:10" hidden="1">
+    <row r="540" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="5" t="s">
         <v>119</v>
       </c>
@@ -25061,7 +25139,7 @@
         <v>88060</v>
       </c>
     </row>
-    <row r="541" spans="1:10" hidden="1">
+    <row r="541" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="5" t="s">
         <v>119</v>
       </c>
@@ -25093,7 +25171,7 @@
         <v>26200</v>
       </c>
     </row>
-    <row r="542" spans="1:10">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A542" s="5" t="s">
         <v>119</v>
       </c>
@@ -25125,7 +25203,7 @@
         <v>29910</v>
       </c>
     </row>
-    <row r="543" spans="1:10" hidden="1">
+    <row r="543" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="5" t="s">
         <v>119</v>
       </c>
@@ -25157,7 +25235,7 @@
         <v>58080</v>
       </c>
     </row>
-    <row r="544" spans="1:10" hidden="1">
+    <row r="544" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="5" t="s">
         <v>120</v>
       </c>
@@ -25189,7 +25267,7 @@
         <v>39690</v>
       </c>
     </row>
-    <row r="545" spans="1:10" hidden="1">
+    <row r="545" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="5" t="s">
         <v>120</v>
       </c>
@@ -25221,7 +25299,7 @@
         <v>89000</v>
       </c>
     </row>
-    <row r="546" spans="1:10" hidden="1">
+    <row r="546" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="5" t="s">
         <v>120</v>
       </c>
@@ -25253,7 +25331,7 @@
         <v>28670</v>
       </c>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" s="5" t="s">
         <v>120</v>
       </c>
@@ -25285,7 +25363,7 @@
         <v>23410</v>
       </c>
     </row>
-    <row r="548" spans="1:10" hidden="1">
+    <row r="548" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="5" t="s">
         <v>120</v>
       </c>
@@ -25317,7 +25395,7 @@
         <v>77960</v>
       </c>
     </row>
-    <row r="549" spans="1:10" hidden="1">
+    <row r="549" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="5" t="s">
         <v>121</v>
       </c>
@@ -25349,7 +25427,7 @@
         <v>58160</v>
       </c>
     </row>
-    <row r="550" spans="1:10" hidden="1">
+    <row r="550" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="5" t="s">
         <v>121</v>
       </c>
@@ -25381,7 +25459,7 @@
         <v>59770</v>
       </c>
     </row>
-    <row r="551" spans="1:10" hidden="1">
+    <row r="551" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="5" t="s">
         <v>121</v>
       </c>
@@ -25413,7 +25491,7 @@
         <v>31420</v>
       </c>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" s="5" t="s">
         <v>121</v>
       </c>
@@ -25445,7 +25523,7 @@
         <v>22860</v>
       </c>
     </row>
-    <row r="553" spans="1:10" hidden="1">
+    <row r="553" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="5" t="s">
         <v>121</v>
       </c>
@@ -25477,7 +25555,7 @@
         <v>189850</v>
       </c>
     </row>
-    <row r="554" spans="1:10" hidden="1">
+    <row r="554" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="5" t="s">
         <v>122</v>
       </c>
@@ -25509,7 +25587,7 @@
         <v>46910</v>
       </c>
     </row>
-    <row r="555" spans="1:10" hidden="1">
+    <row r="555" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="5" t="s">
         <v>122</v>
       </c>
@@ -25541,7 +25619,7 @@
         <v>48370</v>
       </c>
     </row>
-    <row r="556" spans="1:10" hidden="1">
+    <row r="556" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="5" t="s">
         <v>122</v>
       </c>
@@ -25573,7 +25651,7 @@
         <v>31190</v>
       </c>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A557" s="5" t="s">
         <v>122</v>
       </c>
@@ -25605,7 +25683,7 @@
         <v>24840</v>
       </c>
     </row>
-    <row r="558" spans="1:10" hidden="1">
+    <row r="558" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="5" t="s">
         <v>122</v>
       </c>
@@ -25637,7 +25715,7 @@
         <v>41500</v>
       </c>
     </row>
-    <row r="559" spans="1:10" hidden="1">
+    <row r="559" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="5" t="s">
         <v>123</v>
       </c>
@@ -25669,7 +25747,7 @@
         <v>59270</v>
       </c>
     </row>
-    <row r="560" spans="1:10" hidden="1">
+    <row r="560" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="5" t="s">
         <v>123</v>
       </c>
@@ -25701,7 +25779,7 @@
         <v>62110</v>
       </c>
     </row>
-    <row r="561" spans="1:10" hidden="1">
+    <row r="561" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="5" t="s">
         <v>123</v>
       </c>
@@ -25733,7 +25811,7 @@
         <v>36920</v>
       </c>
     </row>
-    <row r="562" spans="1:10">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A562" s="5" t="s">
         <v>123</v>
       </c>
@@ -25765,7 +25843,7 @@
         <v>27830</v>
       </c>
     </row>
-    <row r="563" spans="1:10" hidden="1">
+    <row r="563" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="5" t="s">
         <v>123</v>
       </c>
@@ -25797,7 +25875,7 @@
         <v>73700</v>
       </c>
     </row>
-    <row r="564" spans="1:10" hidden="1">
+    <row r="564" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="5" t="s">
         <v>124</v>
       </c>
@@ -25829,7 +25907,7 @@
         <v>36230</v>
       </c>
     </row>
-    <row r="565" spans="1:10" hidden="1">
+    <row r="565" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="5" t="s">
         <v>124</v>
       </c>
@@ -25861,7 +25939,7 @@
         <v>17570</v>
       </c>
     </row>
-    <row r="566" spans="1:10" hidden="1">
+    <row r="566" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="5" t="s">
         <v>124</v>
       </c>
@@ -25893,7 +25971,7 @@
         <v>26400</v>
       </c>
     </row>
-    <row r="567" spans="1:10">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A567" s="5" t="s">
         <v>124</v>
       </c>
@@ -25925,7 +26003,7 @@
         <v>25640</v>
       </c>
     </row>
-    <row r="568" spans="1:10" hidden="1">
+    <row r="568" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="5" t="s">
         <v>124</v>
       </c>
@@ -25957,7 +26035,7 @@
         <v>51680</v>
       </c>
     </row>
-    <row r="569" spans="1:10" hidden="1">
+    <row r="569" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="5" t="s">
         <v>125</v>
       </c>
@@ -25989,7 +26067,7 @@
         <v>52320</v>
       </c>
     </row>
-    <row r="570" spans="1:10" hidden="1">
+    <row r="570" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="5" t="s">
         <v>125</v>
       </c>
@@ -26021,7 +26099,7 @@
         <v>45570</v>
       </c>
     </row>
-    <row r="571" spans="1:10" hidden="1">
+    <row r="571" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="5" t="s">
         <v>125</v>
       </c>
@@ -26053,7 +26131,7 @@
         <v>25970</v>
       </c>
     </row>
-    <row r="572" spans="1:10">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A572" s="5" t="s">
         <v>125</v>
       </c>
@@ -26085,7 +26163,7 @@
         <v>28200</v>
       </c>
     </row>
-    <row r="573" spans="1:10" hidden="1">
+    <row r="573" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="5" t="s">
         <v>125</v>
       </c>
@@ -26117,7 +26195,7 @@
         <v>47020</v>
       </c>
     </row>
-    <row r="574" spans="1:10" hidden="1">
+    <row r="574" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="5" t="s">
         <v>126</v>
       </c>
@@ -26149,7 +26227,7 @@
         <v>73950</v>
       </c>
     </row>
-    <row r="575" spans="1:10" hidden="1">
+    <row r="575" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="5" t="s">
         <v>126</v>
       </c>
@@ -26181,7 +26259,7 @@
         <v>46740</v>
       </c>
     </row>
-    <row r="576" spans="1:10" hidden="1">
+    <row r="576" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="5" t="s">
         <v>126</v>
       </c>
@@ -26213,7 +26291,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="577" spans="1:10">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A577" s="5" t="s">
         <v>126</v>
       </c>
@@ -26245,7 +26323,7 @@
         <v>29310</v>
       </c>
     </row>
-    <row r="578" spans="1:10" hidden="1">
+    <row r="578" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="5" t="s">
         <v>126</v>
       </c>
@@ -26277,7 +26355,7 @@
         <v>44330</v>
       </c>
     </row>
-    <row r="579" spans="1:10" hidden="1">
+    <row r="579" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="5" t="s">
         <v>127</v>
       </c>
@@ -26309,7 +26387,7 @@
         <v>54840</v>
       </c>
     </row>
-    <row r="580" spans="1:10" hidden="1">
+    <row r="580" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="5" t="s">
         <v>127</v>
       </c>
@@ -26341,7 +26419,7 @@
         <v>31970</v>
       </c>
     </row>
-    <row r="581" spans="1:10" hidden="1">
+    <row r="581" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="5" t="s">
         <v>127</v>
       </c>
@@ -26373,7 +26451,7 @@
         <v>27630</v>
       </c>
     </row>
-    <row r="582" spans="1:10">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A582" s="5" t="s">
         <v>127</v>
       </c>
@@ -26405,7 +26483,7 @@
         <v>31290</v>
       </c>
     </row>
-    <row r="583" spans="1:10" hidden="1">
+    <row r="583" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="5" t="s">
         <v>127</v>
       </c>
@@ -26437,7 +26515,7 @@
         <v>29020</v>
       </c>
     </row>
-    <row r="584" spans="1:10" hidden="1">
+    <row r="584" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="5" t="s">
         <v>128</v>
       </c>
@@ -26469,7 +26547,7 @@
         <v>47800</v>
       </c>
     </row>
-    <row r="585" spans="1:10" hidden="1">
+    <row r="585" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="5" t="s">
         <v>128</v>
       </c>
@@ -26501,7 +26579,7 @@
         <v>41580</v>
       </c>
     </row>
-    <row r="586" spans="1:10" hidden="1">
+    <row r="586" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="5" t="s">
         <v>128</v>
       </c>
@@ -26533,7 +26611,7 @@
         <v>40780</v>
       </c>
     </row>
-    <row r="587" spans="1:10">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A587" s="5" t="s">
         <v>128</v>
       </c>
@@ -26565,7 +26643,7 @@
         <v>33060</v>
       </c>
     </row>
-    <row r="588" spans="1:10" hidden="1">
+    <row r="588" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="5" t="s">
         <v>128</v>
       </c>
@@ -26597,7 +26675,7 @@
         <v>70610</v>
       </c>
     </row>
-    <row r="589" spans="1:10" hidden="1">
+    <row r="589" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="5" t="s">
         <v>129</v>
       </c>
@@ -26629,7 +26707,7 @@
         <v>51830</v>
       </c>
     </row>
-    <row r="590" spans="1:10" hidden="1">
+    <row r="590" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="5" t="s">
         <v>129</v>
       </c>
@@ -26661,7 +26739,7 @@
         <v>118640</v>
       </c>
     </row>
-    <row r="591" spans="1:10" hidden="1">
+    <row r="591" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="5" t="s">
         <v>129</v>
       </c>
@@ -26693,7 +26771,7 @@
         <v>40610</v>
       </c>
     </row>
-    <row r="592" spans="1:10">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A592" s="5" t="s">
         <v>129</v>
       </c>
@@ -26725,7 +26803,7 @@
         <v>34390</v>
       </c>
     </row>
-    <row r="593" spans="1:10" hidden="1">
+    <row r="593" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="5" t="s">
         <v>129</v>
       </c>
@@ -26757,7 +26835,7 @@
         <v>199840</v>
       </c>
     </row>
-    <row r="594" spans="1:10" hidden="1">
+    <row r="594" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="5" t="s">
         <v>130</v>
       </c>
@@ -26789,7 +26867,7 @@
         <v>60730</v>
       </c>
     </row>
-    <row r="595" spans="1:10" hidden="1">
+    <row r="595" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="5" t="s">
         <v>130</v>
       </c>
@@ -26821,7 +26899,7 @@
         <v>64960</v>
       </c>
     </row>
-    <row r="596" spans="1:10" hidden="1">
+    <row r="596" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="5" t="s">
         <v>130</v>
       </c>
@@ -26853,7 +26931,7 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A597" s="5" t="s">
         <v>130</v>
       </c>
@@ -26885,7 +26963,7 @@
         <v>35420</v>
       </c>
     </row>
-    <row r="598" spans="1:10" hidden="1">
+    <row r="598" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="5" t="s">
         <v>130</v>
       </c>
@@ -26917,7 +26995,7 @@
         <v>47020</v>
       </c>
     </row>
-    <row r="599" spans="1:10" hidden="1">
+    <row r="599" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="5" t="s">
         <v>131</v>
       </c>
@@ -26949,7 +27027,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="600" spans="1:10" hidden="1">
+    <row r="600" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="5" t="s">
         <v>131</v>
       </c>
@@ -26981,7 +27059,7 @@
         <v>48480</v>
       </c>
     </row>
-    <row r="601" spans="1:10" hidden="1">
+    <row r="601" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="5" t="s">
         <v>131</v>
       </c>
@@ -27013,7 +27091,7 @@
         <v>32410</v>
       </c>
     </row>
-    <row r="602" spans="1:10">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A602" s="5" t="s">
         <v>131</v>
       </c>
@@ -27045,7 +27123,7 @@
         <v>31050</v>
       </c>
     </row>
-    <row r="603" spans="1:10" hidden="1">
+    <row r="603" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="5" t="s">
         <v>131</v>
       </c>
@@ -27077,7 +27155,7 @@
         <v>35900</v>
       </c>
     </row>
-    <row r="604" spans="1:10" hidden="1">
+    <row r="604" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="5" t="s">
         <v>132</v>
       </c>
@@ -27109,7 +27187,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:10" hidden="1">
+    <row r="605" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="5" t="s">
         <v>132</v>
       </c>
@@ -27141,7 +27219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:10" hidden="1">
+    <row r="606" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="5" t="s">
         <v>132</v>
       </c>
@@ -27173,7 +27251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:10">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A607" s="5" t="s">
         <v>132</v>
       </c>
@@ -27205,7 +27283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="608" spans="1:10" hidden="1">
+    <row r="608" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="10" t="s">
         <v>132</v>
       </c>
@@ -27246,4 +27324,2707 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D192"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>403811</v>
+      </c>
+      <c r="D2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>127895</v>
+      </c>
+      <c r="D3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>106989</v>
+      </c>
+      <c r="D4">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>91763</v>
+      </c>
+      <c r="D5">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>52045</v>
+      </c>
+      <c r="D6">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>33271</v>
+      </c>
+      <c r="D7">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>135226</v>
+      </c>
+      <c r="D8">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>107472</v>
+      </c>
+      <c r="D9">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>80690</v>
+      </c>
+      <c r="D10">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>49780</v>
+      </c>
+      <c r="D11">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>33942</v>
+      </c>
+      <c r="D12">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>54882</v>
+      </c>
+      <c r="D13">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>27550</v>
+      </c>
+      <c r="D14">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>22158</v>
+      </c>
+      <c r="D15">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16">
+        <v>25</v>
+      </c>
+      <c r="C16">
+        <v>15510</v>
+      </c>
+      <c r="D16">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>12030</v>
+      </c>
+      <c r="D17">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B18">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>38732</v>
+      </c>
+      <c r="D18">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19">
+        <v>32</v>
+      </c>
+      <c r="C19">
+        <v>23485</v>
+      </c>
+      <c r="D19">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20">
+        <v>34</v>
+      </c>
+      <c r="C20">
+        <v>21795</v>
+      </c>
+      <c r="D20">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>15400</v>
+      </c>
+      <c r="D21">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B22">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>11615</v>
+      </c>
+      <c r="D22">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>29474</v>
+      </c>
+      <c r="D23">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B24">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>18773</v>
+      </c>
+      <c r="D24">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25">
+        <v>43</v>
+      </c>
+      <c r="C25">
+        <v>16177</v>
+      </c>
+      <c r="D25">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26">
+        <v>45</v>
+      </c>
+      <c r="C26">
+        <v>18629</v>
+      </c>
+      <c r="D26">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>12646</v>
+      </c>
+      <c r="D27">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28">
+        <v>51</v>
+      </c>
+      <c r="C28">
+        <v>17576</v>
+      </c>
+      <c r="D28">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29">
+        <v>52</v>
+      </c>
+      <c r="C29">
+        <v>10729</v>
+      </c>
+      <c r="D29">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30">
+        <v>53</v>
+      </c>
+      <c r="C30">
+        <v>9208</v>
+      </c>
+      <c r="D30">
+        <v>5061</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31">
+        <v>54</v>
+      </c>
+      <c r="C31">
+        <v>10446</v>
+      </c>
+      <c r="D31">
+        <v>5205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32">
+        <v>56</v>
+      </c>
+      <c r="C32">
+        <v>7659</v>
+      </c>
+      <c r="D32">
+        <v>5553</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33">
+        <v>61</v>
+      </c>
+      <c r="C33">
+        <v>10980</v>
+      </c>
+      <c r="D33">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34">
+        <v>62</v>
+      </c>
+      <c r="C34">
+        <v>7743</v>
+      </c>
+      <c r="D34">
+        <v>5698</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35">
+        <v>63</v>
+      </c>
+      <c r="C35">
+        <v>6397</v>
+      </c>
+      <c r="D35">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36">
+        <v>64</v>
+      </c>
+      <c r="C36">
+        <v>6212</v>
+      </c>
+      <c r="D36">
+        <v>6566</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37">
+        <v>65</v>
+      </c>
+      <c r="C37">
+        <v>5000</v>
+      </c>
+      <c r="D37">
+        <v>7397</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>190066</v>
+      </c>
+      <c r="D38">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>146194</v>
+      </c>
+      <c r="D39">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>182</v>
+      </c>
+      <c r="B40">
+        <v>14</v>
+      </c>
+      <c r="C40">
+        <v>110155</v>
+      </c>
+      <c r="D40">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>67346</v>
+      </c>
+      <c r="D41">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>44899</v>
+      </c>
+      <c r="D42">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43">
+        <v>23</v>
+      </c>
+      <c r="C43">
+        <v>51017</v>
+      </c>
+      <c r="D43">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44">
+        <v>24</v>
+      </c>
+      <c r="C44">
+        <v>40924</v>
+      </c>
+      <c r="D44">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>182</v>
+      </c>
+      <c r="B45">
+        <v>25</v>
+      </c>
+      <c r="C45">
+        <v>26230</v>
+      </c>
+      <c r="D45">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46">
+        <v>26</v>
+      </c>
+      <c r="C46">
+        <v>19751</v>
+      </c>
+      <c r="D46">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47">
+        <v>34</v>
+      </c>
+      <c r="C47">
+        <v>37958</v>
+      </c>
+      <c r="D47">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48">
+        <v>35</v>
+      </c>
+      <c r="C48">
+        <v>24597</v>
+      </c>
+      <c r="D48">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49">
+        <v>36</v>
+      </c>
+      <c r="C49">
+        <v>18001</v>
+      </c>
+      <c r="D49">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50">
+        <v>45</v>
+      </c>
+      <c r="C50">
+        <v>29049</v>
+      </c>
+      <c r="D50">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>182</v>
+      </c>
+      <c r="B51">
+        <v>46</v>
+      </c>
+      <c r="C51">
+        <v>18838</v>
+      </c>
+      <c r="D51">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52">
+        <v>56</v>
+      </c>
+      <c r="C52">
+        <v>12607</v>
+      </c>
+      <c r="D52">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53">
+        <v>123</v>
+      </c>
+      <c r="C53">
+        <v>49129</v>
+      </c>
+      <c r="D53">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54">
+        <v>124</v>
+      </c>
+      <c r="C54">
+        <v>38140</v>
+      </c>
+      <c r="D54">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55">
+        <v>125</v>
+      </c>
+      <c r="C55">
+        <v>26828</v>
+      </c>
+      <c r="D55">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56">
+        <v>126</v>
+      </c>
+      <c r="C56">
+        <v>21098</v>
+      </c>
+      <c r="D56">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57">
+        <v>132</v>
+      </c>
+      <c r="C57">
+        <v>35950</v>
+      </c>
+      <c r="D57">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58">
+        <v>134</v>
+      </c>
+      <c r="C58">
+        <v>31240</v>
+      </c>
+      <c r="D58">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>183</v>
+      </c>
+      <c r="B59">
+        <v>135</v>
+      </c>
+      <c r="C59">
+        <v>22655</v>
+      </c>
+      <c r="D59">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>17609</v>
+      </c>
+      <c r="D60">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61">
+        <v>142</v>
+      </c>
+      <c r="C61">
+        <v>26990</v>
+      </c>
+      <c r="D61">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62">
+        <v>143</v>
+      </c>
+      <c r="C62">
+        <v>23083</v>
+      </c>
+      <c r="D62">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63">
+        <v>145</v>
+      </c>
+      <c r="C63">
+        <v>16510</v>
+      </c>
+      <c r="D63">
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64">
+        <v>146</v>
+      </c>
+      <c r="C64">
+        <v>14097</v>
+      </c>
+      <c r="D64">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B65">
+        <v>152</v>
+      </c>
+      <c r="C65">
+        <v>15959</v>
+      </c>
+      <c r="D65">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66">
+        <v>153</v>
+      </c>
+      <c r="C66">
+        <v>13830</v>
+      </c>
+      <c r="D66">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67">
+        <v>154</v>
+      </c>
+      <c r="C67">
+        <v>11193</v>
+      </c>
+      <c r="D67">
+        <v>5203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>183</v>
+      </c>
+      <c r="B68">
+        <v>156</v>
+      </c>
+      <c r="C68">
+        <v>8788</v>
+      </c>
+      <c r="D68">
+        <v>6101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>183</v>
+      </c>
+      <c r="B69">
+        <v>162</v>
+      </c>
+      <c r="C69">
+        <v>10799</v>
+      </c>
+      <c r="D69">
+        <v>6037</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70">
+        <v>163</v>
+      </c>
+      <c r="C70">
+        <v>9080</v>
+      </c>
+      <c r="D70">
+        <v>6415</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71">
+        <v>164</v>
+      </c>
+      <c r="C71">
+        <v>8009</v>
+      </c>
+      <c r="D71">
+        <v>7623</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>183</v>
+      </c>
+      <c r="B72">
+        <v>165</v>
+      </c>
+      <c r="C72">
+        <v>6031</v>
+      </c>
+      <c r="D72">
+        <v>8717</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>183</v>
+      </c>
+      <c r="B73">
+        <v>213</v>
+      </c>
+      <c r="C73">
+        <v>17964</v>
+      </c>
+      <c r="D73">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74">
+        <v>214</v>
+      </c>
+      <c r="C74">
+        <v>15719</v>
+      </c>
+      <c r="D74">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75">
+        <v>215</v>
+      </c>
+      <c r="C75">
+        <v>11629</v>
+      </c>
+      <c r="D75">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>183</v>
+      </c>
+      <c r="B76">
+        <v>216</v>
+      </c>
+      <c r="C76">
+        <v>9549</v>
+      </c>
+      <c r="D76">
+        <v>6273</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>183</v>
+      </c>
+      <c r="B77">
+        <v>231</v>
+      </c>
+      <c r="C77">
+        <v>8521</v>
+      </c>
+      <c r="D77">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78">
+        <v>234</v>
+      </c>
+      <c r="C78">
+        <v>7726</v>
+      </c>
+      <c r="D78">
+        <v>6922</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>183</v>
+      </c>
+      <c r="B79">
+        <v>235</v>
+      </c>
+      <c r="C79">
+        <v>6040</v>
+      </c>
+      <c r="D79">
+        <v>8429</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>183</v>
+      </c>
+      <c r="B80">
+        <v>236</v>
+      </c>
+      <c r="C80">
+        <v>5253</v>
+      </c>
+      <c r="D80">
+        <v>10036</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81">
+        <v>241</v>
+      </c>
+      <c r="C81">
+        <v>7227</v>
+      </c>
+      <c r="D81">
+        <v>7957</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82">
+        <v>243</v>
+      </c>
+      <c r="C82">
+        <v>6080</v>
+      </c>
+      <c r="D82">
+        <v>9067</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83">
+        <v>245</v>
+      </c>
+      <c r="C83">
+        <v>4783</v>
+      </c>
+      <c r="D83">
+        <v>10142</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>183</v>
+      </c>
+      <c r="B84">
+        <v>246</v>
+      </c>
+      <c r="C84">
+        <v>4060</v>
+      </c>
+      <c r="D84">
+        <v>11337</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>183</v>
+      </c>
+      <c r="B85">
+        <v>251</v>
+      </c>
+      <c r="C85">
+        <v>4682</v>
+      </c>
+      <c r="D85">
+        <v>10982</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>183</v>
+      </c>
+      <c r="B86">
+        <v>253</v>
+      </c>
+      <c r="C86">
+        <v>4281</v>
+      </c>
+      <c r="D86">
+        <v>12175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87">
+        <v>254</v>
+      </c>
+      <c r="C87">
+        <v>3586</v>
+      </c>
+      <c r="D87">
+        <v>13683</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88">
+        <v>256</v>
+      </c>
+      <c r="C88">
+        <v>2957</v>
+      </c>
+      <c r="D88">
+        <v>15255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89">
+        <v>261</v>
+      </c>
+      <c r="C89">
+        <v>3628</v>
+      </c>
+      <c r="D89">
+        <v>14901</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90">
+        <v>263</v>
+      </c>
+      <c r="C90">
+        <v>3309</v>
+      </c>
+      <c r="D90">
+        <v>15894</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91">
+        <v>264</v>
+      </c>
+      <c r="C91">
+        <v>2795</v>
+      </c>
+      <c r="D91">
+        <v>16378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92">
+        <v>265</v>
+      </c>
+      <c r="C92">
+        <v>2284</v>
+      </c>
+      <c r="D92">
+        <v>19922</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93">
+        <v>312</v>
+      </c>
+      <c r="C93">
+        <v>9860</v>
+      </c>
+      <c r="D93">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94">
+        <v>314</v>
+      </c>
+      <c r="C94">
+        <v>11861</v>
+      </c>
+      <c r="D94">
+        <v>5105</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95">
+        <v>315</v>
+      </c>
+      <c r="C95">
+        <v>9466</v>
+      </c>
+      <c r="D95">
+        <v>5821</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96">
+        <v>316</v>
+      </c>
+      <c r="C96">
+        <v>7540</v>
+      </c>
+      <c r="D96">
+        <v>7523</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>183</v>
+      </c>
+      <c r="B97">
+        <v>321</v>
+      </c>
+      <c r="C97">
+        <v>6598</v>
+      </c>
+      <c r="D97">
+        <v>8661</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>183</v>
+      </c>
+      <c r="B98">
+        <v>324</v>
+      </c>
+      <c r="C98">
+        <v>6740</v>
+      </c>
+      <c r="D98">
+        <v>9659</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99">
+        <v>325</v>
+      </c>
+      <c r="C99">
+        <v>5478</v>
+      </c>
+      <c r="D99">
+        <v>11330</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B100">
+        <v>326</v>
+      </c>
+      <c r="C100">
+        <v>4658</v>
+      </c>
+      <c r="D100">
+        <v>12945</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101">
+        <v>341</v>
+      </c>
+      <c r="C101">
+        <v>6374</v>
+      </c>
+      <c r="D101">
+        <v>7848</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>183</v>
+      </c>
+      <c r="B102">
+        <v>342</v>
+      </c>
+      <c r="C102">
+        <v>5354</v>
+      </c>
+      <c r="D102">
+        <v>11088</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103">
+        <v>345</v>
+      </c>
+      <c r="C103">
+        <v>5417</v>
+      </c>
+      <c r="D103">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>183</v>
+      </c>
+      <c r="B104">
+        <v>346</v>
+      </c>
+      <c r="C104">
+        <v>4638</v>
+      </c>
+      <c r="D104">
+        <v>11013</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105">
+        <v>351</v>
+      </c>
+      <c r="C105">
+        <v>4562</v>
+      </c>
+      <c r="D105">
+        <v>11204</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>183</v>
+      </c>
+      <c r="B106">
+        <v>352</v>
+      </c>
+      <c r="C106">
+        <v>3820</v>
+      </c>
+      <c r="D106">
+        <v>14492</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>183</v>
+      </c>
+      <c r="B107">
+        <v>354</v>
+      </c>
+      <c r="C107">
+        <v>3854</v>
+      </c>
+      <c r="D107">
+        <v>13787</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>183</v>
+      </c>
+      <c r="B108">
+        <v>356</v>
+      </c>
+      <c r="C108">
+        <v>3153</v>
+      </c>
+      <c r="D108">
+        <v>14630</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109">
+        <v>361</v>
+      </c>
+      <c r="C109">
+        <v>3273</v>
+      </c>
+      <c r="D109">
+        <v>14661</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>183</v>
+      </c>
+      <c r="B110">
+        <v>362</v>
+      </c>
+      <c r="C110">
+        <v>2924</v>
+      </c>
+      <c r="D110">
+        <v>18853</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111">
+        <v>364</v>
+      </c>
+      <c r="C111">
+        <v>2960</v>
+      </c>
+      <c r="D111">
+        <v>16644</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>183</v>
+      </c>
+      <c r="B112">
+        <v>365</v>
+      </c>
+      <c r="C112">
+        <v>2455</v>
+      </c>
+      <c r="D112">
+        <v>18763</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>183</v>
+      </c>
+      <c r="B113">
+        <v>412</v>
+      </c>
+      <c r="C113">
+        <v>8320</v>
+      </c>
+      <c r="D113">
+        <v>6150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>183</v>
+      </c>
+      <c r="B114">
+        <v>413</v>
+      </c>
+      <c r="C114">
+        <v>6661</v>
+      </c>
+      <c r="D114">
+        <v>7544</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>183</v>
+      </c>
+      <c r="B115">
+        <v>415</v>
+      </c>
+      <c r="C115">
+        <v>7891</v>
+      </c>
+      <c r="D115">
+        <v>7157</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>183</v>
+      </c>
+      <c r="B116">
+        <v>416</v>
+      </c>
+      <c r="C116">
+        <v>6599</v>
+      </c>
+      <c r="D116">
+        <v>8660</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>183</v>
+      </c>
+      <c r="B117">
+        <v>421</v>
+      </c>
+      <c r="C117">
+        <v>6018</v>
+      </c>
+      <c r="D117">
+        <v>9567</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>183</v>
+      </c>
+      <c r="B118">
+        <v>423</v>
+      </c>
+      <c r="C118">
+        <v>4181</v>
+      </c>
+      <c r="D118">
+        <v>12544</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>183</v>
+      </c>
+      <c r="B119">
+        <v>425</v>
+      </c>
+      <c r="C119">
+        <v>4521</v>
+      </c>
+      <c r="D119">
+        <v>12499</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>183</v>
+      </c>
+      <c r="B120">
+        <v>426</v>
+      </c>
+      <c r="C120">
+        <v>4051</v>
+      </c>
+      <c r="D120">
+        <v>14130</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>183</v>
+      </c>
+      <c r="B121">
+        <v>431</v>
+      </c>
+      <c r="C121">
+        <v>4612</v>
+      </c>
+      <c r="D121">
+        <v>11044</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>183</v>
+      </c>
+      <c r="B122">
+        <v>432</v>
+      </c>
+      <c r="C122">
+        <v>3629</v>
+      </c>
+      <c r="D122">
+        <v>14286</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>183</v>
+      </c>
+      <c r="B123">
+        <v>435</v>
+      </c>
+      <c r="C123">
+        <v>4211</v>
+      </c>
+      <c r="D123">
+        <v>13605</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>183</v>
+      </c>
+      <c r="B124">
+        <v>436</v>
+      </c>
+      <c r="C124">
+        <v>3714</v>
+      </c>
+      <c r="D124">
+        <v>15497</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>183</v>
+      </c>
+      <c r="B125">
+        <v>451</v>
+      </c>
+      <c r="C125">
+        <v>5875</v>
+      </c>
+      <c r="D125">
+        <v>9490</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>183</v>
+      </c>
+      <c r="B126">
+        <v>452</v>
+      </c>
+      <c r="C126">
+        <v>4413</v>
+      </c>
+      <c r="D126">
+        <v>12290</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>183</v>
+      </c>
+      <c r="B127">
+        <v>453</v>
+      </c>
+      <c r="C127">
+        <v>3698</v>
+      </c>
+      <c r="D127">
+        <v>14674</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>183</v>
+      </c>
+      <c r="B128">
+        <v>456</v>
+      </c>
+      <c r="C128">
+        <v>4631</v>
+      </c>
+      <c r="D128">
+        <v>10803</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>183</v>
+      </c>
+      <c r="B129">
+        <v>461</v>
+      </c>
+      <c r="C129">
+        <v>3865</v>
+      </c>
+      <c r="D129">
+        <v>13763</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>183</v>
+      </c>
+      <c r="B130">
+        <v>462</v>
+      </c>
+      <c r="C130">
+        <v>3023</v>
+      </c>
+      <c r="D130">
+        <v>17026</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>183</v>
+      </c>
+      <c r="B131">
+        <v>463</v>
+      </c>
+      <c r="C131">
+        <v>2643</v>
+      </c>
+      <c r="D131">
+        <v>19180</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>183</v>
+      </c>
+      <c r="B132">
+        <v>465</v>
+      </c>
+      <c r="C132">
+        <v>3099</v>
+      </c>
+      <c r="D132">
+        <v>16089</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>183</v>
+      </c>
+      <c r="B133">
+        <v>512</v>
+      </c>
+      <c r="C133">
+        <v>5086</v>
+      </c>
+      <c r="D133">
+        <v>11212</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>183</v>
+      </c>
+      <c r="B134">
+        <v>513</v>
+      </c>
+      <c r="C134">
+        <v>4474</v>
+      </c>
+      <c r="D134">
+        <v>12166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>183</v>
+      </c>
+      <c r="B135">
+        <v>514</v>
+      </c>
+      <c r="C135">
+        <v>4012</v>
+      </c>
+      <c r="D135">
+        <v>14038</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>183</v>
+      </c>
+      <c r="B136">
+        <v>516</v>
+      </c>
+      <c r="C136">
+        <v>4001</v>
+      </c>
+      <c r="D136">
+        <v>14827</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>183</v>
+      </c>
+      <c r="B137">
+        <v>521</v>
+      </c>
+      <c r="C137">
+        <v>3501</v>
+      </c>
+      <c r="D137">
+        <v>15474</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>183</v>
+      </c>
+      <c r="B138">
+        <v>523</v>
+      </c>
+      <c r="C138">
+        <v>2589</v>
+      </c>
+      <c r="D138">
+        <v>18533</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>183</v>
+      </c>
+      <c r="B139">
+        <v>524</v>
+      </c>
+      <c r="C139">
+        <v>2199</v>
+      </c>
+      <c r="D139">
+        <v>20569</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>183</v>
+      </c>
+      <c r="B140">
+        <v>526</v>
+      </c>
+      <c r="C140">
+        <v>2438</v>
+      </c>
+      <c r="D140">
+        <v>21262</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>183</v>
+      </c>
+      <c r="B141">
+        <v>531</v>
+      </c>
+      <c r="C141">
+        <v>2705</v>
+      </c>
+      <c r="D141">
+        <v>16989</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>183</v>
+      </c>
+      <c r="B142">
+        <v>532</v>
+      </c>
+      <c r="C142">
+        <v>2286</v>
+      </c>
+      <c r="D142">
+        <v>20403</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>183</v>
+      </c>
+      <c r="B143">
+        <v>534</v>
+      </c>
+      <c r="C143">
+        <v>2154</v>
+      </c>
+      <c r="D143">
+        <v>22936</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>183</v>
+      </c>
+      <c r="B144">
+        <v>536</v>
+      </c>
+      <c r="C144">
+        <v>2057</v>
+      </c>
+      <c r="D144">
+        <v>22789</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>183</v>
+      </c>
+      <c r="B145">
+        <v>541</v>
+      </c>
+      <c r="C145">
+        <v>3210</v>
+      </c>
+      <c r="D145">
+        <v>17833</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>183</v>
+      </c>
+      <c r="B146">
+        <v>542</v>
+      </c>
+      <c r="C146">
+        <v>2493</v>
+      </c>
+      <c r="D146">
+        <v>21282</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>183</v>
+      </c>
+      <c r="B147">
+        <v>543</v>
+      </c>
+      <c r="C147">
+        <v>1969</v>
+      </c>
+      <c r="D147">
+        <v>25358</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>183</v>
+      </c>
+      <c r="B148">
+        <v>546</v>
+      </c>
+      <c r="C148">
+        <v>2760</v>
+      </c>
+      <c r="D148">
+        <v>20419</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>183</v>
+      </c>
+      <c r="B149">
+        <v>561</v>
+      </c>
+      <c r="C149">
+        <v>2404</v>
+      </c>
+      <c r="D149">
+        <v>21262</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>183</v>
+      </c>
+      <c r="B150">
+        <v>562</v>
+      </c>
+      <c r="C150">
+        <v>1928</v>
+      </c>
+      <c r="D150">
+        <v>24143</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>183</v>
+      </c>
+      <c r="B151">
+        <v>563</v>
+      </c>
+      <c r="C151">
+        <v>1652</v>
+      </c>
+      <c r="D151">
+        <v>25630</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>183</v>
+      </c>
+      <c r="B152">
+        <v>564</v>
+      </c>
+      <c r="C152">
+        <v>1649</v>
+      </c>
+      <c r="D152">
+        <v>25866</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>183</v>
+      </c>
+      <c r="B153">
+        <v>612</v>
+      </c>
+      <c r="C153">
+        <v>3377</v>
+      </c>
+      <c r="D153">
+        <v>14745</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>183</v>
+      </c>
+      <c r="B154">
+        <v>613</v>
+      </c>
+      <c r="C154">
+        <v>2965</v>
+      </c>
+      <c r="D154">
+        <v>16029</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>183</v>
+      </c>
+      <c r="B155">
+        <v>614</v>
+      </c>
+      <c r="C155">
+        <v>2590</v>
+      </c>
+      <c r="D155">
+        <v>18697</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>183</v>
+      </c>
+      <c r="B156">
+        <v>615</v>
+      </c>
+      <c r="C156">
+        <v>2040</v>
+      </c>
+      <c r="D156">
+        <v>21070</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>183</v>
+      </c>
+      <c r="B157">
+        <v>621</v>
+      </c>
+      <c r="C157">
+        <v>2498</v>
+      </c>
+      <c r="D157">
+        <v>19723</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>183</v>
+      </c>
+      <c r="B158">
+        <v>623</v>
+      </c>
+      <c r="C158">
+        <v>1981</v>
+      </c>
+      <c r="D158">
+        <v>22328</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>183</v>
+      </c>
+      <c r="B159">
+        <v>624</v>
+      </c>
+      <c r="C159">
+        <v>1781</v>
+      </c>
+      <c r="D159">
+        <v>23956</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>183</v>
+      </c>
+      <c r="B160">
+        <v>625</v>
+      </c>
+      <c r="C160">
+        <v>1473</v>
+      </c>
+      <c r="D160">
+        <v>29173</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>183</v>
+      </c>
+      <c r="B161">
+        <v>631</v>
+      </c>
+      <c r="C161">
+        <v>1890</v>
+      </c>
+      <c r="D161">
+        <v>22385</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>183</v>
+      </c>
+      <c r="B162">
+        <v>632</v>
+      </c>
+      <c r="C162">
+        <v>1578</v>
+      </c>
+      <c r="D162">
+        <v>24704</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>183</v>
+      </c>
+      <c r="B163">
+        <v>634</v>
+      </c>
+      <c r="C163">
+        <v>1604</v>
+      </c>
+      <c r="D163">
+        <v>26446</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>183</v>
+      </c>
+      <c r="B164">
+        <v>635</v>
+      </c>
+      <c r="C164">
+        <v>1320</v>
+      </c>
+      <c r="D164">
+        <v>29180</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>183</v>
+      </c>
+      <c r="B165">
+        <v>641</v>
+      </c>
+      <c r="C165">
+        <v>1908</v>
+      </c>
+      <c r="D165">
+        <v>23706</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>183</v>
+      </c>
+      <c r="B166">
+        <v>642</v>
+      </c>
+      <c r="C166">
+        <v>1587</v>
+      </c>
+      <c r="D166">
+        <v>26465</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>183</v>
+      </c>
+      <c r="B167">
+        <v>643</v>
+      </c>
+      <c r="C167">
+        <v>1416</v>
+      </c>
+      <c r="D167">
+        <v>30124</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>183</v>
+      </c>
+      <c r="B168">
+        <v>645</v>
+      </c>
+      <c r="C168">
+        <v>1292</v>
+      </c>
+      <c r="D168">
+        <v>28851</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>183</v>
+      </c>
+      <c r="B169">
+        <v>651</v>
+      </c>
+      <c r="C169">
+        <v>1517</v>
+      </c>
+      <c r="D169">
+        <v>29333</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>183</v>
+      </c>
+      <c r="B170">
+        <v>652</v>
+      </c>
+      <c r="C170">
+        <v>1260</v>
+      </c>
+      <c r="D170">
+        <v>31604</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>183</v>
+      </c>
+      <c r="B171">
+        <v>653</v>
+      </c>
+      <c r="C171">
+        <v>1065</v>
+      </c>
+      <c r="D171">
+        <v>33478</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>183</v>
+      </c>
+      <c r="B172">
+        <v>654</v>
+      </c>
+      <c r="C172">
+        <v>1137</v>
+      </c>
+      <c r="D172">
+        <v>32435</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>184</v>
+      </c>
+      <c r="B173">
+        <v>123</v>
+      </c>
+      <c r="C173">
+        <v>127891</v>
+      </c>
+      <c r="D173">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174">
+        <v>124</v>
+      </c>
+      <c r="C174">
+        <v>102382</v>
+      </c>
+      <c r="D174">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>184</v>
+      </c>
+      <c r="B175">
+        <v>125</v>
+      </c>
+      <c r="C175">
+        <v>67650</v>
+      </c>
+      <c r="D175">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+      <c r="B176">
+        <v>126</v>
+      </c>
+      <c r="C176">
+        <v>50897</v>
+      </c>
+      <c r="D176">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177">
+        <v>134</v>
+      </c>
+      <c r="C177">
+        <v>83813</v>
+      </c>
+      <c r="D177">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>184</v>
+      </c>
+      <c r="B178">
+        <v>135</v>
+      </c>
+      <c r="C178">
+        <v>57681</v>
+      </c>
+      <c r="D178">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179">
+        <v>136</v>
+      </c>
+      <c r="C179">
+        <v>42348</v>
+      </c>
+      <c r="D179">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>184</v>
+      </c>
+      <c r="B180">
+        <v>145</v>
+      </c>
+      <c r="C180">
+        <v>48672</v>
+      </c>
+      <c r="D180">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181">
+        <v>146</v>
+      </c>
+      <c r="C181">
+        <v>37052</v>
+      </c>
+      <c r="D181">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>184</v>
+      </c>
+      <c r="B182">
+        <v>156</v>
+      </c>
+      <c r="C182">
+        <v>24745</v>
+      </c>
+      <c r="D182">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>184</v>
+      </c>
+      <c r="B183">
+        <v>234</v>
+      </c>
+      <c r="C183">
+        <v>33687</v>
+      </c>
+      <c r="D183">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184">
+        <v>235</v>
+      </c>
+      <c r="C184">
+        <v>24479</v>
+      </c>
+      <c r="D184">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>236</v>
+      </c>
+      <c r="C185">
+        <v>19681</v>
+      </c>
+      <c r="D185">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>245</v>
+      </c>
+      <c r="C186">
+        <v>21976</v>
+      </c>
+      <c r="D186">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>184</v>
+      </c>
+      <c r="B187">
+        <v>246</v>
+      </c>
+      <c r="C187">
+        <v>17277</v>
+      </c>
+      <c r="D187">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>184</v>
+      </c>
+      <c r="B188">
+        <v>256</v>
+      </c>
+      <c r="C188">
+        <v>12296</v>
+      </c>
+      <c r="D188">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>184</v>
+      </c>
+      <c r="B189">
+        <v>345</v>
+      </c>
+      <c r="C189">
+        <v>21267</v>
+      </c>
+      <c r="D189">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>184</v>
+      </c>
+      <c r="B190">
+        <v>346</v>
+      </c>
+      <c r="C190">
+        <v>16949</v>
+      </c>
+      <c r="D190">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>184</v>
+      </c>
+      <c r="B191">
+        <v>356</v>
+      </c>
+      <c r="C191">
+        <v>11659</v>
+      </c>
+      <c r="D191">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>184</v>
+      </c>
+      <c r="B192">
+        <v>456</v>
+      </c>
+      <c r="C192">
+        <v>14305</v>
+      </c>
+      <c r="D192">
+        <v>2921</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>